--- a/Documentos/Outros/BES3543 - Status Comissionamento.xlsx
+++ b/Documentos/Outros/BES3543 - Status Comissionamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felipe Andrade\Documents\GitHub\BES3543_Valgroup\Documentos\Outros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C87B2E59-DE15-4014-B5AF-4F7FC975B6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41ABC144-C716-4C98-9E91-45FFBA059BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B185CC03-3427-41D4-BC34-550D574748A1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="32">
   <si>
     <t>Energização</t>
   </si>
@@ -114,6 +114,27 @@
   </si>
   <si>
     <t>terça-feira</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>ip</t>
+  </si>
+  <si>
+    <t>Concluido</t>
+  </si>
+  <si>
+    <t>Em progressos</t>
+  </si>
+  <si>
+    <t>Com pendência</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>IP</t>
   </si>
 </sst>
 </file>
@@ -135,7 +156,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,12 +165,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -157,36 +202,103 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color theme="0"/>
+      </left>
+      <right style="thick">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -516,290 +628,812 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8318353E-AB7E-469D-AE80-D90D194AED40}">
-  <dimension ref="B2:S27"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="32.44140625" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" style="3" customWidth="1"/>
-    <col min="4" max="19" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="30.21875" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" style="1" customWidth="1"/>
+    <col min="3" max="18" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="C2" s="3" t="s">
+    <row r="1" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+    </row>
+    <row r="4" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="F5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="L5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="M5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="R5" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="C3" s="4">
+    <row r="6" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="4">
         <v>46281</v>
       </c>
-      <c r="D3" s="4">
+      <c r="C6" s="4">
         <v>46282</v>
       </c>
-      <c r="E3" s="4">
+      <c r="D6" s="4">
         <v>46283</v>
       </c>
-      <c r="F3" s="4">
+      <c r="E6" s="7">
         <v>46284</v>
       </c>
-      <c r="G3" s="4">
+      <c r="F6" s="7">
         <v>46285</v>
       </c>
-      <c r="H3" s="4">
+      <c r="G6" s="4">
         <v>46286</v>
       </c>
-      <c r="I3" s="4">
+      <c r="H6" s="4">
         <v>46287</v>
       </c>
-      <c r="J3" s="4">
+      <c r="I6" s="4">
         <v>46288</v>
       </c>
-      <c r="K3" s="4">
+      <c r="J6" s="4">
         <v>46289</v>
       </c>
-      <c r="L3" s="4">
+      <c r="K6" s="4">
         <v>46290</v>
       </c>
-      <c r="M3" s="4">
+      <c r="L6" s="7">
         <v>46291</v>
       </c>
-      <c r="N3" s="4">
+      <c r="M6" s="7">
         <v>46292</v>
       </c>
-      <c r="O3" s="4">
+      <c r="N6" s="4">
         <v>46293</v>
       </c>
-      <c r="P3" s="4">
+      <c r="O6" s="4">
         <v>46294</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="P6" s="4">
         <v>46295</v>
       </c>
-      <c r="R3" s="4">
+      <c r="Q6" s="4">
         <v>46296</v>
       </c>
-      <c r="S3" s="4">
+      <c r="R6" s="4">
         <v>46297</v>
       </c>
     </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+    <row r="7" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+      <c r="B9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
+      <c r="B10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
+      <c r="B11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
+      <c r="B12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+    </row>
+    <row r="14" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+      <c r="B14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+    </row>
+    <row r="15" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
+      <c r="B15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+    </row>
+    <row r="16" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
+      <c r="B16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+    </row>
+    <row r="17" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+    </row>
+    <row r="18" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+      <c r="B18" s="3"/>
+      <c r="C18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+    </row>
+    <row r="19" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+    </row>
+    <row r="20" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
+      <c r="B20" s="3"/>
+      <c r="C20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+    </row>
+    <row r="21" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="1" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+    </row>
+    <row r="22" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+    </row>
+    <row r="23" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="1" t="s">
+      <c r="B23" s="3"/>
+      <c r="C23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+    </row>
+    <row r="24" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
+      <c r="B24" s="3"/>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+    </row>
+    <row r="25" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
+      <c r="B25" s="3"/>
+      <c r="C25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+    </row>
+    <row r="26" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+      <c r="B26" s="3"/>
+      <c r="C26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+    </row>
+    <row r="27" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="1" t="s">
+      <c r="B27" s="3"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+    </row>
+    <row r="28" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="1" t="s">
+      <c r="B28" s="3"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+    </row>
+    <row r="29" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
+      <c r="B29" s="3"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+    </row>
+    <row r="30" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
         <v>14</v>
       </c>
-    </row>
+      <c r="B30" s="3"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+    </row>
+    <row r="31" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B7:R30">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"ip"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Documentos/Outros/BES3543 - Status Comissionamento.xlsx
+++ b/Documentos/Outros/BES3543 - Status Comissionamento.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felipe Andrade\Documents\GitHub\BES3543_Valgroup\Documentos\Outros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41ABC144-C716-4C98-9E91-45FFBA059BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2893B36-1AF7-4DB7-8F65-263150DC4951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B185CC03-3427-41D4-BC34-550D574748A1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Pendencias " sheetId="2" r:id="rId1"/>
+    <sheet name="Comissionamento" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="50">
   <si>
     <t>Energização</t>
   </si>
@@ -122,26 +123,80 @@
     <t>ip</t>
   </si>
   <si>
-    <t>Concluido</t>
-  </si>
-  <si>
-    <t>Em progressos</t>
-  </si>
-  <si>
-    <t>Com pendência</t>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
     <t>IP</t>
+  </si>
+  <si>
+    <t>Pendencias</t>
+  </si>
+  <si>
+    <t>Melhoria na rotina de Est. Entrada</t>
+  </si>
+  <si>
+    <t>Melhoria na rotina de Est. Envolvedor</t>
+  </si>
+  <si>
+    <t>Lógica Posicionador</t>
+  </si>
+  <si>
+    <t>Inserir botão Máquina Acoplada na IHM</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Data de Conclusão</t>
+  </si>
+  <si>
+    <t>Melhoria na rotina de Pesagem</t>
+  </si>
+  <si>
+    <t>Validação de Tela de Contagem e Dados</t>
+  </si>
+  <si>
+    <t>Separação de Botões de Comando Porta e Botoeira Central</t>
+  </si>
+  <si>
+    <t>Observações</t>
+  </si>
+  <si>
+    <t>Teste Troca de Sinais Máquina Valgroup</t>
+  </si>
+  <si>
+    <t>Teste de ciclo real para função de Inspeção</t>
+  </si>
+  <si>
+    <t>Inserir numero de Inspeções na IHM</t>
+  </si>
+  <si>
+    <t>Inserir comando para fazer inspeção no próximo ciclo</t>
+  </si>
+  <si>
+    <t>ni</t>
+  </si>
+  <si>
+    <t>Concluido (ok)</t>
+  </si>
+  <si>
+    <t>Em progressos (ip)</t>
+  </si>
+  <si>
+    <t>Não Iniciada (ni)</t>
+  </si>
+  <si>
+    <t>Com pendência (cp)</t>
+  </si>
+  <si>
+    <t>Fazer intertravamento para que o ciclo só comece após término de todos os Homes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,8 +210,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,6 +256,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -221,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -256,11 +331,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF00B050"/>
@@ -268,6 +352,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -292,9 +386,12 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFFFFF00"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -627,30 +724,1881 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9205E96B-FC89-41B7-B235-ECC3A58C3003}">
+  <dimension ref="B1:E293"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="82.44140625" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="19.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="62.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46283</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46283</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46288</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46288</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <v>46289</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="2"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="2"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="2"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="2"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="2"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="2"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="2"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="2"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="2"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="2"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="2"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="2"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="2"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="2"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="2"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="2"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="2"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="2"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="2"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="2"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="2"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="2"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="2"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="2"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="2"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="2"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="2"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="2"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="2"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="2"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="2"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="2"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="2"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="2"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="2"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="2"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="2"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="2"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="2"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="2"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="2"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B57" s="2"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="2"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="2"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="2"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="2"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="2"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="2"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B64" s="2"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B65" s="2"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="2"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B67" s="2"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B68" s="2"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="2"/>
+    </row>
+    <row r="69" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B69" s="2"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B70" s="2"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="2"/>
+    </row>
+    <row r="71" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B71" s="2"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B72" s="2"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="2"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="74" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="2"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="2"/>
+    </row>
+    <row r="75" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B75" s="2"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B76" s="2"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B77" s="2"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="2"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="2"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="2"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="2"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="2"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B83" s="2"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B84" s="2"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="2"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B86" s="2"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B87" s="2"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="2"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B89" s="2"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="2"/>
+    </row>
+    <row r="90" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B90" s="2"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="2"/>
+    </row>
+    <row r="91" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B91" s="2"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="2"/>
+    </row>
+    <row r="92" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="2"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="2"/>
+    </row>
+    <row r="93" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B93" s="2"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B94" s="2"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B95" s="2"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B96" s="2"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B97" s="2"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="2"/>
+    </row>
+    <row r="98" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B98" s="2"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="2"/>
+    </row>
+    <row r="99" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B99" s="2"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B100" s="2"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="2"/>
+    </row>
+    <row r="101" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="2"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="2"/>
+    </row>
+    <row r="102" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B102" s="2"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="2"/>
+    </row>
+    <row r="103" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B103" s="2"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="2"/>
+    </row>
+    <row r="104" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B104" s="2"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="2"/>
+    </row>
+    <row r="105" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B105" s="2"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="2"/>
+    </row>
+    <row r="106" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B106" s="2"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="2"/>
+    </row>
+    <row r="107" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B107" s="2"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="2"/>
+    </row>
+    <row r="108" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="2"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="2"/>
+    </row>
+    <row r="109" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B109" s="2"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="2"/>
+    </row>
+    <row r="110" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B110" s="2"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="2"/>
+    </row>
+    <row r="111" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B111" s="2"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="2"/>
+    </row>
+    <row r="112" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B112" s="2"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="2"/>
+    </row>
+    <row r="113" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B113" s="2"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="2"/>
+    </row>
+    <row r="114" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B114" s="2"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="2"/>
+    </row>
+    <row r="115" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B115" s="2"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="2"/>
+    </row>
+    <row r="116" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B116" s="2"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="2"/>
+    </row>
+    <row r="117" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B117" s="2"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="2"/>
+    </row>
+    <row r="118" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="2"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="2"/>
+    </row>
+    <row r="119" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="2"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="2"/>
+    </row>
+    <row r="120" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="2"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="2"/>
+    </row>
+    <row r="121" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B121" s="2"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="2"/>
+    </row>
+    <row r="122" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B122" s="2"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="2"/>
+    </row>
+    <row r="123" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B123" s="2"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="2"/>
+    </row>
+    <row r="124" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="2"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="2"/>
+    </row>
+    <row r="125" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B125" s="2"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="2"/>
+    </row>
+    <row r="126" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B126" s="2"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="2"/>
+    </row>
+    <row r="127" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B127" s="2"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="2"/>
+    </row>
+    <row r="128" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B128" s="2"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="2"/>
+    </row>
+    <row r="129" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B129" s="2"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="2"/>
+    </row>
+    <row r="130" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B130" s="2"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="2"/>
+    </row>
+    <row r="131" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B131" s="2"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="2"/>
+    </row>
+    <row r="132" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B132" s="2"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="2"/>
+    </row>
+    <row r="133" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B133" s="2"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="2"/>
+    </row>
+    <row r="134" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B134" s="2"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="2"/>
+    </row>
+    <row r="135" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B135" s="2"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="2"/>
+    </row>
+    <row r="136" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B136" s="2"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="2"/>
+    </row>
+    <row r="137" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B137" s="2"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="2"/>
+    </row>
+    <row r="138" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B138" s="2"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="2"/>
+    </row>
+    <row r="139" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B139" s="2"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="2"/>
+    </row>
+    <row r="140" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B140" s="2"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="2"/>
+    </row>
+    <row r="141" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B141" s="2"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="2"/>
+    </row>
+    <row r="142" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B142" s="2"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="2"/>
+    </row>
+    <row r="143" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B143" s="2"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="2"/>
+    </row>
+    <row r="144" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B144" s="2"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="2"/>
+    </row>
+    <row r="145" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B145" s="2"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="2"/>
+    </row>
+    <row r="146" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B146" s="2"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="2"/>
+    </row>
+    <row r="147" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="2"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="2"/>
+    </row>
+    <row r="148" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B148" s="2"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="2"/>
+    </row>
+    <row r="149" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="2"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="2"/>
+    </row>
+    <row r="150" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B150" s="2"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B151" s="2"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="2"/>
+    </row>
+    <row r="152" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="2"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="2"/>
+    </row>
+    <row r="153" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="2"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="2"/>
+    </row>
+    <row r="154" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B154" s="2"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="2"/>
+    </row>
+    <row r="155" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B155" s="2"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="2"/>
+    </row>
+    <row r="156" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="2"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="2"/>
+    </row>
+    <row r="157" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="2"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="2"/>
+    </row>
+    <row r="158" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B158" s="2"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="2"/>
+    </row>
+    <row r="159" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B159" s="2"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="2"/>
+    </row>
+    <row r="160" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B160" s="2"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="2"/>
+    </row>
+    <row r="161" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B161" s="2"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="2"/>
+    </row>
+    <row r="162" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B162" s="2"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="2"/>
+    </row>
+    <row r="163" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B163" s="2"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="2"/>
+    </row>
+    <row r="164" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B164" s="2"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="2"/>
+    </row>
+    <row r="165" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B165" s="2"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="2"/>
+    </row>
+    <row r="166" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B166" s="2"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="2"/>
+    </row>
+    <row r="167" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B167" s="2"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="2"/>
+    </row>
+    <row r="168" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B168" s="2"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="2"/>
+    </row>
+    <row r="169" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B169" s="2"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="2"/>
+    </row>
+    <row r="170" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B170" s="2"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="2"/>
+    </row>
+    <row r="171" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B171" s="2"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="2"/>
+    </row>
+    <row r="172" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B172" s="2"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="2"/>
+    </row>
+    <row r="173" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B173" s="2"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="2"/>
+    </row>
+    <row r="174" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B174" s="2"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="2"/>
+    </row>
+    <row r="175" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B175" s="2"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="2"/>
+    </row>
+    <row r="176" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B176" s="2"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="2"/>
+    </row>
+    <row r="177" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B177" s="2"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="2"/>
+    </row>
+    <row r="178" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B178" s="2"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="2"/>
+    </row>
+    <row r="179" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B179" s="2"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="2"/>
+    </row>
+    <row r="180" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B180" s="2"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="2"/>
+    </row>
+    <row r="181" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B181" s="2"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="2"/>
+    </row>
+    <row r="182" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B182" s="2"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="2"/>
+    </row>
+    <row r="183" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B183" s="2"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="2"/>
+    </row>
+    <row r="184" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B184" s="2"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="2"/>
+    </row>
+    <row r="185" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B185" s="2"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="2"/>
+    </row>
+    <row r="186" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B186" s="2"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="2"/>
+    </row>
+    <row r="187" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B187" s="2"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="2"/>
+    </row>
+    <row r="188" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B188" s="2"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="2"/>
+    </row>
+    <row r="189" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B189" s="2"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
+      <c r="E189" s="2"/>
+    </row>
+    <row r="190" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B190" s="2"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+      <c r="E190" s="2"/>
+    </row>
+    <row r="191" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B191" s="2"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="2"/>
+    </row>
+    <row r="192" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B192" s="2"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="2"/>
+    </row>
+    <row r="193" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B193" s="2"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
+      <c r="E193" s="2"/>
+    </row>
+    <row r="194" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B194" s="2"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="2"/>
+    </row>
+    <row r="195" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B195" s="2"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+      <c r="E195" s="2"/>
+    </row>
+    <row r="196" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B196" s="2"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+      <c r="E196" s="2"/>
+    </row>
+    <row r="197" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B197" s="2"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
+      <c r="E197" s="2"/>
+    </row>
+    <row r="198" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B198" s="2"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+      <c r="E198" s="2"/>
+    </row>
+    <row r="199" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B199" s="2"/>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3"/>
+      <c r="E199" s="2"/>
+    </row>
+    <row r="200" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B200" s="2"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
+      <c r="E200" s="2"/>
+    </row>
+    <row r="201" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B201" s="2"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
+      <c r="E201" s="2"/>
+    </row>
+    <row r="202" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B202" s="2"/>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
+      <c r="E202" s="2"/>
+    </row>
+    <row r="203" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B203" s="2"/>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3"/>
+      <c r="E203" s="2"/>
+    </row>
+    <row r="204" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B204" s="2"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+      <c r="E204" s="2"/>
+    </row>
+    <row r="205" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B205" s="2"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+      <c r="E205" s="2"/>
+    </row>
+    <row r="206" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B206" s="2"/>
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
+      <c r="E206" s="2"/>
+    </row>
+    <row r="207" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B207" s="2"/>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
+      <c r="E207" s="2"/>
+    </row>
+    <row r="208" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B208" s="2"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="2"/>
+    </row>
+    <row r="209" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B209" s="2"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+      <c r="E209" s="2"/>
+    </row>
+    <row r="210" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B210" s="2"/>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
+      <c r="E210" s="2"/>
+    </row>
+    <row r="211" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B211" s="2"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
+      <c r="E211" s="2"/>
+    </row>
+    <row r="212" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B212" s="2"/>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
+      <c r="E212" s="2"/>
+    </row>
+    <row r="213" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B213" s="2"/>
+      <c r="C213" s="3"/>
+      <c r="D213" s="3"/>
+      <c r="E213" s="2"/>
+    </row>
+    <row r="214" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B214" s="2"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
+      <c r="E214" s="2"/>
+    </row>
+    <row r="215" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B215" s="2"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
+      <c r="E215" s="2"/>
+    </row>
+    <row r="216" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B216" s="2"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
+      <c r="E216" s="2"/>
+    </row>
+    <row r="217" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B217" s="2"/>
+      <c r="C217" s="3"/>
+      <c r="D217" s="3"/>
+      <c r="E217" s="2"/>
+    </row>
+    <row r="218" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B218" s="2"/>
+      <c r="C218" s="3"/>
+      <c r="D218" s="3"/>
+      <c r="E218" s="2"/>
+    </row>
+    <row r="219" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B219" s="2"/>
+      <c r="C219" s="3"/>
+      <c r="D219" s="3"/>
+      <c r="E219" s="2"/>
+    </row>
+    <row r="220" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B220" s="2"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="3"/>
+      <c r="E220" s="2"/>
+    </row>
+    <row r="221" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B221" s="2"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="3"/>
+      <c r="E221" s="2"/>
+    </row>
+    <row r="222" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B222" s="2"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3"/>
+      <c r="E222" s="2"/>
+    </row>
+    <row r="223" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B223" s="2"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="3"/>
+      <c r="E223" s="2"/>
+    </row>
+    <row r="224" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B224" s="2"/>
+      <c r="C224" s="3"/>
+      <c r="D224" s="3"/>
+      <c r="E224" s="2"/>
+    </row>
+    <row r="225" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B225" s="2"/>
+      <c r="C225" s="3"/>
+      <c r="D225" s="3"/>
+      <c r="E225" s="2"/>
+    </row>
+    <row r="226" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B226" s="2"/>
+      <c r="C226" s="3"/>
+      <c r="D226" s="3"/>
+      <c r="E226" s="2"/>
+    </row>
+    <row r="227" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B227" s="2"/>
+      <c r="C227" s="3"/>
+      <c r="D227" s="3"/>
+      <c r="E227" s="2"/>
+    </row>
+    <row r="228" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B228" s="2"/>
+      <c r="C228" s="3"/>
+      <c r="D228" s="3"/>
+      <c r="E228" s="2"/>
+    </row>
+    <row r="229" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B229" s="2"/>
+      <c r="C229" s="3"/>
+      <c r="D229" s="3"/>
+      <c r="E229" s="2"/>
+    </row>
+    <row r="230" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B230" s="2"/>
+      <c r="C230" s="3"/>
+      <c r="D230" s="3"/>
+      <c r="E230" s="2"/>
+    </row>
+    <row r="231" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B231" s="2"/>
+      <c r="C231" s="3"/>
+      <c r="D231" s="3"/>
+      <c r="E231" s="2"/>
+    </row>
+    <row r="232" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B232" s="2"/>
+      <c r="C232" s="3"/>
+      <c r="D232" s="3"/>
+      <c r="E232" s="2"/>
+    </row>
+    <row r="233" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B233" s="2"/>
+      <c r="C233" s="3"/>
+      <c r="D233" s="3"/>
+      <c r="E233" s="2"/>
+    </row>
+    <row r="234" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B234" s="2"/>
+      <c r="C234" s="3"/>
+      <c r="D234" s="3"/>
+      <c r="E234" s="2"/>
+    </row>
+    <row r="235" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B235" s="2"/>
+      <c r="C235" s="3"/>
+      <c r="D235" s="3"/>
+      <c r="E235" s="2"/>
+    </row>
+    <row r="236" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B236" s="2"/>
+      <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
+      <c r="E236" s="2"/>
+    </row>
+    <row r="237" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B237" s="2"/>
+      <c r="C237" s="3"/>
+      <c r="D237" s="3"/>
+      <c r="E237" s="2"/>
+    </row>
+    <row r="238" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B238" s="2"/>
+      <c r="C238" s="3"/>
+      <c r="D238" s="3"/>
+      <c r="E238" s="2"/>
+    </row>
+    <row r="239" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B239" s="2"/>
+      <c r="C239" s="3"/>
+      <c r="D239" s="3"/>
+      <c r="E239" s="2"/>
+    </row>
+    <row r="240" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B240" s="2"/>
+      <c r="C240" s="3"/>
+      <c r="D240" s="3"/>
+      <c r="E240" s="2"/>
+    </row>
+    <row r="241" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B241" s="2"/>
+      <c r="C241" s="3"/>
+      <c r="D241" s="3"/>
+      <c r="E241" s="2"/>
+    </row>
+    <row r="242" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B242" s="2"/>
+      <c r="C242" s="3"/>
+      <c r="D242" s="3"/>
+      <c r="E242" s="2"/>
+    </row>
+    <row r="243" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B243" s="2"/>
+      <c r="C243" s="3"/>
+      <c r="D243" s="3"/>
+      <c r="E243" s="2"/>
+    </row>
+    <row r="244" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B244" s="2"/>
+      <c r="C244" s="3"/>
+      <c r="D244" s="3"/>
+      <c r="E244" s="2"/>
+    </row>
+    <row r="245" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B245" s="2"/>
+      <c r="C245" s="3"/>
+      <c r="D245" s="3"/>
+      <c r="E245" s="2"/>
+    </row>
+    <row r="246" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B246" s="2"/>
+      <c r="C246" s="3"/>
+      <c r="D246" s="3"/>
+      <c r="E246" s="2"/>
+    </row>
+    <row r="247" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B247" s="2"/>
+      <c r="C247" s="3"/>
+      <c r="D247" s="3"/>
+      <c r="E247" s="2"/>
+    </row>
+    <row r="248" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B248" s="2"/>
+      <c r="C248" s="3"/>
+      <c r="D248" s="3"/>
+      <c r="E248" s="2"/>
+    </row>
+    <row r="249" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B249" s="2"/>
+      <c r="C249" s="3"/>
+      <c r="D249" s="3"/>
+      <c r="E249" s="2"/>
+    </row>
+    <row r="250" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B250" s="2"/>
+      <c r="C250" s="3"/>
+      <c r="D250" s="3"/>
+      <c r="E250" s="2"/>
+    </row>
+    <row r="251" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B251" s="2"/>
+      <c r="C251" s="3"/>
+      <c r="D251" s="3"/>
+      <c r="E251" s="2"/>
+    </row>
+    <row r="252" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B252" s="2"/>
+      <c r="C252" s="3"/>
+      <c r="D252" s="3"/>
+      <c r="E252" s="2"/>
+    </row>
+    <row r="253" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B253" s="2"/>
+      <c r="C253" s="3"/>
+      <c r="D253" s="3"/>
+      <c r="E253" s="2"/>
+    </row>
+    <row r="254" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B254" s="2"/>
+      <c r="C254" s="3"/>
+      <c r="D254" s="3"/>
+      <c r="E254" s="2"/>
+    </row>
+    <row r="255" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B255" s="2"/>
+      <c r="C255" s="3"/>
+      <c r="D255" s="3"/>
+      <c r="E255" s="2"/>
+    </row>
+    <row r="256" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B256" s="2"/>
+      <c r="C256" s="3"/>
+      <c r="D256" s="3"/>
+      <c r="E256" s="2"/>
+    </row>
+    <row r="257" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B257" s="2"/>
+      <c r="C257" s="3"/>
+      <c r="D257" s="3"/>
+      <c r="E257" s="2"/>
+    </row>
+    <row r="258" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B258" s="2"/>
+      <c r="C258" s="3"/>
+      <c r="D258" s="3"/>
+      <c r="E258" s="2"/>
+    </row>
+    <row r="259" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B259" s="2"/>
+      <c r="C259" s="3"/>
+      <c r="D259" s="3"/>
+      <c r="E259" s="2"/>
+    </row>
+    <row r="260" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B260" s="2"/>
+      <c r="C260" s="3"/>
+      <c r="D260" s="3"/>
+      <c r="E260" s="2"/>
+    </row>
+    <row r="261" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B261" s="2"/>
+      <c r="C261" s="3"/>
+      <c r="D261" s="3"/>
+      <c r="E261" s="2"/>
+    </row>
+    <row r="262" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B262" s="2"/>
+      <c r="C262" s="3"/>
+      <c r="D262" s="3"/>
+      <c r="E262" s="2"/>
+    </row>
+    <row r="263" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B263" s="2"/>
+      <c r="C263" s="3"/>
+      <c r="D263" s="3"/>
+      <c r="E263" s="2"/>
+    </row>
+    <row r="264" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B264" s="2"/>
+      <c r="C264" s="3"/>
+      <c r="D264" s="3"/>
+      <c r="E264" s="2"/>
+    </row>
+    <row r="265" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B265" s="2"/>
+      <c r="C265" s="3"/>
+      <c r="D265" s="3"/>
+      <c r="E265" s="2"/>
+    </row>
+    <row r="266" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B266" s="2"/>
+      <c r="C266" s="3"/>
+      <c r="D266" s="3"/>
+      <c r="E266" s="2"/>
+    </row>
+    <row r="267" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B267" s="2"/>
+      <c r="C267" s="3"/>
+      <c r="D267" s="3"/>
+      <c r="E267" s="2"/>
+    </row>
+    <row r="268" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B268" s="2"/>
+      <c r="C268" s="3"/>
+      <c r="D268" s="3"/>
+      <c r="E268" s="2"/>
+    </row>
+    <row r="269" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B269" s="2"/>
+      <c r="C269" s="3"/>
+      <c r="D269" s="3"/>
+      <c r="E269" s="2"/>
+    </row>
+    <row r="270" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B270" s="2"/>
+      <c r="C270" s="3"/>
+      <c r="D270" s="3"/>
+      <c r="E270" s="2"/>
+    </row>
+    <row r="271" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B271" s="2"/>
+      <c r="C271" s="3"/>
+      <c r="D271" s="3"/>
+      <c r="E271" s="2"/>
+    </row>
+    <row r="272" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B272" s="2"/>
+      <c r="C272" s="3"/>
+      <c r="D272" s="3"/>
+      <c r="E272" s="2"/>
+    </row>
+    <row r="273" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B273" s="2"/>
+      <c r="C273" s="3"/>
+      <c r="D273" s="3"/>
+      <c r="E273" s="2"/>
+    </row>
+    <row r="274" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B274" s="2"/>
+      <c r="C274" s="3"/>
+      <c r="D274" s="3"/>
+      <c r="E274" s="2"/>
+    </row>
+    <row r="275" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B275" s="2"/>
+      <c r="C275" s="3"/>
+      <c r="D275" s="3"/>
+      <c r="E275" s="2"/>
+    </row>
+    <row r="276" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B276" s="2"/>
+      <c r="C276" s="3"/>
+      <c r="D276" s="3"/>
+      <c r="E276" s="2"/>
+    </row>
+    <row r="277" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B277" s="2"/>
+      <c r="C277" s="3"/>
+      <c r="D277" s="3"/>
+      <c r="E277" s="2"/>
+    </row>
+    <row r="278" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B278" s="2"/>
+      <c r="C278" s="3"/>
+      <c r="D278" s="3"/>
+      <c r="E278" s="2"/>
+    </row>
+    <row r="279" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B279" s="2"/>
+      <c r="C279" s="3"/>
+      <c r="D279" s="3"/>
+      <c r="E279" s="2"/>
+    </row>
+    <row r="280" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B280" s="2"/>
+      <c r="C280" s="3"/>
+      <c r="D280" s="3"/>
+      <c r="E280" s="2"/>
+    </row>
+    <row r="281" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B281" s="2"/>
+      <c r="C281" s="3"/>
+      <c r="D281" s="3"/>
+      <c r="E281" s="2"/>
+    </row>
+    <row r="282" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B282" s="2"/>
+      <c r="C282" s="3"/>
+      <c r="D282" s="3"/>
+      <c r="E282" s="2"/>
+    </row>
+    <row r="283" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B283" s="2"/>
+      <c r="C283" s="3"/>
+      <c r="D283" s="3"/>
+      <c r="E283" s="2"/>
+    </row>
+    <row r="284" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B284" s="2"/>
+      <c r="C284" s="3"/>
+      <c r="D284" s="3"/>
+      <c r="E284" s="2"/>
+    </row>
+    <row r="285" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B285" s="2"/>
+      <c r="C285" s="3"/>
+      <c r="D285" s="3"/>
+      <c r="E285" s="2"/>
+    </row>
+    <row r="286" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B286" s="2"/>
+      <c r="C286" s="3"/>
+      <c r="D286" s="3"/>
+      <c r="E286" s="2"/>
+    </row>
+    <row r="287" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B287" s="2"/>
+      <c r="C287" s="3"/>
+      <c r="D287" s="3"/>
+      <c r="E287" s="2"/>
+    </row>
+    <row r="288" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B288" s="2"/>
+      <c r="C288" s="3"/>
+      <c r="D288" s="3"/>
+      <c r="E288" s="2"/>
+    </row>
+    <row r="289" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B289" s="2"/>
+      <c r="C289" s="3"/>
+      <c r="D289" s="3"/>
+      <c r="E289" s="2"/>
+    </row>
+    <row r="290" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B290" s="2"/>
+      <c r="C290" s="3"/>
+      <c r="D290" s="3"/>
+      <c r="E290" s="2"/>
+    </row>
+    <row r="291" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B291" s="2"/>
+      <c r="C291" s="3"/>
+      <c r="D291" s="3"/>
+      <c r="E291" s="2"/>
+    </row>
+    <row r="292" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B292" s="2"/>
+      <c r="C292" s="3"/>
+      <c r="D292" s="3"/>
+      <c r="E292" s="2"/>
+    </row>
+    <row r="293" spans="2:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <conditionalFormatting sqref="C3:C292">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"ni"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"ip"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8318353E-AB7E-469D-AE80-D90D194AED40}">
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.21875" customWidth="1"/>
     <col min="2" max="2" width="14.5546875" style="1" customWidth="1"/>
-    <col min="3" max="18" width="14.5546875" customWidth="1"/>
+    <col min="3" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="18" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="10"/>
       <c r="C1" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -660,10 +2608,8 @@
     </row>
     <row r="2" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -682,157 +2628,163 @@
     </row>
     <row r="3" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
+      <c r="B4" s="4">
+        <v>46281</v>
+      </c>
+      <c r="C4" s="4">
+        <v>46282</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46283</v>
+      </c>
+      <c r="E4" s="7">
+        <v>46284</v>
+      </c>
+      <c r="F4" s="7">
+        <v>46285</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46286</v>
+      </c>
+      <c r="H4" s="4">
+        <v>46287</v>
+      </c>
+      <c r="I4" s="4">
+        <v>46288</v>
+      </c>
+      <c r="J4" s="4">
+        <v>46289</v>
+      </c>
+      <c r="K4" s="4">
+        <v>46290</v>
+      </c>
+      <c r="L4" s="7">
+        <v>46291</v>
+      </c>
+      <c r="M4" s="7">
+        <v>46292</v>
+      </c>
+      <c r="N4" s="4">
+        <v>46293</v>
+      </c>
+      <c r="O4" s="4">
+        <v>46294</v>
+      </c>
+      <c r="P4" s="4">
+        <v>46295</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>46296</v>
+      </c>
+      <c r="R4" s="4">
+        <v>46297</v>
+      </c>
     </row>
     <row r="5" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
+      <c r="A5" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="4">
-        <v>46281</v>
-      </c>
-      <c r="C6" s="4">
-        <v>46282</v>
-      </c>
-      <c r="D6" s="4">
-        <v>46283</v>
-      </c>
-      <c r="E6" s="7">
-        <v>46284</v>
-      </c>
-      <c r="F6" s="7">
-        <v>46285</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46286</v>
-      </c>
-      <c r="H6" s="4">
-        <v>46287</v>
-      </c>
-      <c r="I6" s="4">
-        <v>46288</v>
-      </c>
-      <c r="J6" s="4">
-        <v>46289</v>
-      </c>
-      <c r="K6" s="4">
-        <v>46290</v>
-      </c>
-      <c r="L6" s="7">
-        <v>46291</v>
-      </c>
-      <c r="M6" s="7">
-        <v>46292</v>
-      </c>
-      <c r="N6" s="4">
-        <v>46293</v>
-      </c>
-      <c r="O6" s="4">
-        <v>46294</v>
-      </c>
-      <c r="P6" s="4">
-        <v>46295</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>46296</v>
-      </c>
-      <c r="R6" s="4">
-        <v>46297</v>
-      </c>
+      <c r="A6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>25</v>
@@ -856,12 +2808,14 @@
     </row>
     <row r="8" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="D8" s="2"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -879,8 +2833,8 @@
       <c r="R8" s="2"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>2</v>
+      <c r="A9" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>25</v>
@@ -903,14 +2857,14 @@
       <c r="R9" s="2"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>30</v>
+      <c r="A10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="8"/>
@@ -930,7 +2884,7 @@
     </row>
     <row r="11" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>25</v>
@@ -954,13 +2908,13 @@
     </row>
     <row r="12" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="8"/>
@@ -979,13 +2933,15 @@
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>6</v>
+      <c r="A13" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
@@ -1004,14 +2960,12 @@
     </row>
     <row r="14" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>30</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
@@ -1029,14 +2983,12 @@
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="A15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="3"/>
       <c r="C15" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="8"/>
@@ -1056,12 +3008,12 @@
     </row>
     <row r="16" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D16" s="2"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -1079,17 +3031,21 @@
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
-        <v>17</v>
+      <c r="A17" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
-      <c r="G17" s="2"/>
+      <c r="G17" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -1104,16 +3060,20 @@
     </row>
     <row r="18" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
-      <c r="G18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -1127,19 +3087,21 @@
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
-        <v>9</v>
+      <c r="A19" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
-      <c r="G19" s="2"/>
+      <c r="G19" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -1154,18 +3116,20 @@
     </row>
     <row r="20" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -1179,19 +3143,21 @@
       <c r="R20" s="2"/>
     </row>
     <row r="21" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
-        <v>13</v>
+      <c r="A21" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
-      <c r="G21" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -1206,18 +3172,20 @@
     </row>
     <row r="22" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
-      <c r="G22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -1231,19 +3199,21 @@
       <c r="R22" s="2"/>
     </row>
     <row r="23" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="5" t="s">
-        <v>10</v>
+      <c r="A23" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
-      <c r="G23" s="2"/>
+      <c r="G23" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -1258,19 +3228,23 @@
     </row>
     <row r="24" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="G24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -1283,20 +3257,20 @@
       <c r="R24" s="2"/>
     </row>
     <row r="25" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
-        <v>13</v>
+      <c r="A25" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
+      <c r="G25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -1310,19 +3284,19 @@
     </row>
     <row r="26" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1335,16 +3309,20 @@
       <c r="R26" s="2"/>
     </row>
     <row r="27" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
-        <v>11</v>
+      <c r="A27" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
+      <c r="G27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -1358,15 +3336,19 @@
     </row>
     <row r="28" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
+      <c r="G28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -1378,54 +3360,10 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-    </row>
-    <row r="30" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-    </row>
-    <row r="31" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B7:R30">
+  <conditionalFormatting sqref="B5:R28">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"ip"</formula>
     </cfRule>

--- a/Documentos/Outros/BES3543 - Status Comissionamento.xlsx
+++ b/Documentos/Outros/BES3543 - Status Comissionamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felipe Andrade\Documents\GitHub\BES3543_Valgroup\Documentos\Outros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2893B36-1AF7-4DB7-8F65-263150DC4951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CF07BC-4E1C-4B47-8E5D-80BDD3A418F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B185CC03-3427-41D4-BC34-550D574748A1}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="53">
   <si>
     <t>Energização</t>
   </si>
@@ -190,6 +190,15 @@
   </si>
   <si>
     <t>Fazer intertravamento para que o ciclo só comece após término de todos os Homes</t>
+  </si>
+  <si>
+    <t>Testar Etiquetadora</t>
+  </si>
+  <si>
+    <t>Colocar na IHM o campo para editar Posição de Corte do Giro do Envolvedor</t>
+  </si>
+  <si>
+    <t>Rever todos os Alarmes de todas as rotinas</t>
   </si>
 </sst>
 </file>
@@ -331,14 +340,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -729,7 +738,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="82.44140625" customWidth="1"/>
+    <col min="2" max="2" width="82.44140625" style="16" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" style="1"/>
     <col min="4" max="4" width="19.21875" style="1" customWidth="1"/>
     <col min="5" max="5" width="62.21875" customWidth="1"/>
@@ -737,21 +746,21 @@
   <sheetData>
     <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -763,7 +772,7 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -775,7 +784,7 @@
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -785,7 +794,7 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -797,7 +806,7 @@
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -809,7 +818,7 @@
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -819,7 +828,7 @@
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -829,7 +838,7 @@
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -839,7 +848,7 @@
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -851,7 +860,7 @@
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -861,7 +870,7 @@
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -871,7 +880,7 @@
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -881,1669 +890,1679 @@
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="2"/>
-      <c r="C15" s="3"/>
+      <c r="B15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="D15" s="3"/>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="2"/>
-      <c r="C16" s="3"/>
+      <c r="B16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="12"/>
       <c r="D16" s="3"/>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="2"/>
-      <c r="C17" s="3"/>
+      <c r="B17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="2"/>
+      <c r="B18" s="5"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="2"/>
+      <c r="B19" s="5"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="2"/>
+      <c r="B20" s="5"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="2"/>
+      <c r="B21" s="5"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="2"/>
+      <c r="B22" s="5"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="2"/>
     </row>
     <row r="23" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="2"/>
+      <c r="B23" s="5"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="2"/>
+      <c r="B24" s="5"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="2"/>
     </row>
     <row r="25" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="2"/>
+      <c r="B25" s="5"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="2"/>
+      <c r="B26" s="5"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="2"/>
     </row>
     <row r="27" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="2"/>
+      <c r="B27" s="5"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="2"/>
+      <c r="B28" s="5"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="2"/>
+      <c r="B29" s="5"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="2"/>
+      <c r="B30" s="5"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="2"/>
+      <c r="B31" s="5"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="2"/>
+      <c r="B32" s="5"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="2"/>
     </row>
     <row r="33" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="2"/>
+      <c r="B33" s="5"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="2"/>
     </row>
     <row r="34" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="2"/>
+      <c r="B34" s="5"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="2"/>
+      <c r="B35" s="5"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="2"/>
+      <c r="B36" s="5"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="2"/>
     </row>
     <row r="37" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="2"/>
+      <c r="B37" s="5"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="2"/>
     </row>
     <row r="38" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="2"/>
+      <c r="B38" s="5"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="2"/>
     </row>
     <row r="39" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="2"/>
+      <c r="B39" s="5"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="2"/>
     </row>
     <row r="40" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="2"/>
+      <c r="B40" s="5"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="2"/>
     </row>
     <row r="41" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="2"/>
+      <c r="B41" s="5"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="2"/>
+      <c r="B42" s="5"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="2"/>
     </row>
     <row r="43" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="2"/>
+      <c r="B43" s="5"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="2"/>
     </row>
     <row r="44" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="2"/>
+      <c r="B44" s="5"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="2"/>
     </row>
     <row r="45" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="2"/>
+      <c r="B45" s="5"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="2"/>
     </row>
     <row r="46" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="2"/>
+      <c r="B46" s="5"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="2"/>
+      <c r="B47" s="5"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="2"/>
     </row>
     <row r="48" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="2"/>
+      <c r="B48" s="5"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="2"/>
     </row>
     <row r="49" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="2"/>
+      <c r="B49" s="5"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="2"/>
     </row>
     <row r="50" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="2"/>
+      <c r="B50" s="5"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="2"/>
+      <c r="B51" s="5"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="2"/>
     </row>
     <row r="52" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="2"/>
+      <c r="B52" s="5"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="2"/>
     </row>
     <row r="53" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="2"/>
+      <c r="B53" s="5"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="2"/>
     </row>
     <row r="54" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="2"/>
+      <c r="B54" s="5"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="2"/>
     </row>
     <row r="55" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="2"/>
+      <c r="B55" s="5"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="2"/>
     </row>
     <row r="56" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="2"/>
+      <c r="B56" s="5"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="2"/>
     </row>
     <row r="57" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="2"/>
+      <c r="B57" s="5"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="2"/>
     </row>
     <row r="58" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="2"/>
+      <c r="B58" s="5"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="2"/>
     </row>
     <row r="59" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="2"/>
+      <c r="B59" s="5"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="2"/>
+      <c r="B60" s="5"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="2"/>
+      <c r="B61" s="5"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="2"/>
     </row>
     <row r="62" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="2"/>
+      <c r="B62" s="5"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="2"/>
+      <c r="B63" s="5"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="2"/>
     </row>
     <row r="64" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="2"/>
+      <c r="B64" s="5"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="2"/>
     </row>
     <row r="65" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="2"/>
+      <c r="B65" s="5"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="2"/>
     </row>
     <row r="66" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="2"/>
+      <c r="B66" s="5"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="2"/>
     </row>
     <row r="67" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="2"/>
+      <c r="B67" s="5"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="2"/>
     </row>
     <row r="68" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="2"/>
+      <c r="B68" s="5"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="2"/>
     </row>
     <row r="69" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="2"/>
+      <c r="B69" s="5"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="2"/>
     </row>
     <row r="70" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="2"/>
+      <c r="B70" s="5"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="2"/>
     </row>
     <row r="71" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="2"/>
+      <c r="B71" s="5"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="2"/>
+      <c r="B72" s="5"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="2"/>
     </row>
     <row r="73" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="2"/>
+      <c r="B73" s="5"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="2"/>
+      <c r="B74" s="5"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="2"/>
+      <c r="B75" s="5"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="2"/>
+      <c r="B76" s="5"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="2"/>
     </row>
     <row r="77" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="2"/>
+      <c r="B77" s="5"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="2"/>
+      <c r="B78" s="5"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="2"/>
     </row>
     <row r="79" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="2"/>
+      <c r="B79" s="5"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="2"/>
+      <c r="B80" s="5"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="2"/>
     </row>
     <row r="81" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="2"/>
+      <c r="B81" s="5"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="2"/>
     </row>
     <row r="82" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B82" s="2"/>
+      <c r="B82" s="5"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="2"/>
     </row>
     <row r="83" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="2"/>
+      <c r="B83" s="5"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="2"/>
+      <c r="B84" s="5"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="2"/>
     </row>
     <row r="85" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="2"/>
+      <c r="B85" s="5"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="2"/>
     </row>
     <row r="86" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="2"/>
+      <c r="B86" s="5"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="2"/>
     </row>
     <row r="87" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="2"/>
+      <c r="B87" s="5"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="2"/>
     </row>
     <row r="88" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="2"/>
+      <c r="B88" s="5"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="2"/>
     </row>
     <row r="89" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="2"/>
+      <c r="B89" s="5"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="2"/>
+      <c r="B90" s="5"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="2"/>
+      <c r="B91" s="5"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="2"/>
+      <c r="B92" s="5"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="2"/>
     </row>
     <row r="93" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="2"/>
+      <c r="B93" s="5"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="2"/>
     </row>
     <row r="94" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B94" s="2"/>
+      <c r="B94" s="5"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="2"/>
     </row>
     <row r="95" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="2"/>
+      <c r="B95" s="5"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="2"/>
     </row>
     <row r="96" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="2"/>
+      <c r="B96" s="5"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="2"/>
     </row>
     <row r="97" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="2"/>
+      <c r="B97" s="5"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="2"/>
     </row>
     <row r="98" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="2"/>
+      <c r="B98" s="5"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="2"/>
+      <c r="B99" s="5"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="2"/>
     </row>
     <row r="100" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B100" s="2"/>
+      <c r="B100" s="5"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="2"/>
     </row>
     <row r="101" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="2"/>
+      <c r="B101" s="5"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="2"/>
     </row>
     <row r="102" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B102" s="2"/>
+      <c r="B102" s="5"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="2"/>
     </row>
     <row r="103" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="2"/>
+      <c r="B103" s="5"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="2"/>
+      <c r="B104" s="5"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B105" s="2"/>
+      <c r="B105" s="5"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="2"/>
     </row>
     <row r="106" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B106" s="2"/>
+      <c r="B106" s="5"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B107" s="2"/>
+      <c r="B107" s="5"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="2"/>
     </row>
     <row r="108" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="2"/>
+      <c r="B108" s="5"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="2"/>
     </row>
     <row r="109" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="2"/>
+      <c r="B109" s="5"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="2"/>
     </row>
     <row r="110" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B110" s="2"/>
+      <c r="B110" s="5"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="2"/>
     </row>
     <row r="111" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B111" s="2"/>
+      <c r="B111" s="5"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="2"/>
     </row>
     <row r="112" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B112" s="2"/>
+      <c r="B112" s="5"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="2"/>
     </row>
     <row r="113" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B113" s="2"/>
+      <c r="B113" s="5"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="2"/>
     </row>
     <row r="114" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="2"/>
+      <c r="B114" s="5"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="2"/>
     </row>
     <row r="115" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="2"/>
+      <c r="B115" s="5"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="2"/>
     </row>
     <row r="116" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B116" s="2"/>
+      <c r="B116" s="5"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="2"/>
     </row>
     <row r="117" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B117" s="2"/>
+      <c r="B117" s="5"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="2"/>
     </row>
     <row r="118" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B118" s="2"/>
+      <c r="B118" s="5"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="2"/>
     </row>
     <row r="119" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="2"/>
+      <c r="B119" s="5"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="2"/>
     </row>
     <row r="120" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="2"/>
+      <c r="B120" s="5"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="2"/>
     </row>
     <row r="121" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B121" s="2"/>
+      <c r="B121" s="5"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="2"/>
     </row>
     <row r="122" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B122" s="2"/>
+      <c r="B122" s="5"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="2"/>
     </row>
     <row r="123" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B123" s="2"/>
+      <c r="B123" s="5"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="2"/>
     </row>
     <row r="124" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="2"/>
+      <c r="B124" s="5"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="2"/>
     </row>
     <row r="125" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="2"/>
+      <c r="B125" s="5"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="2"/>
     </row>
     <row r="126" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B126" s="2"/>
+      <c r="B126" s="5"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="2"/>
     </row>
     <row r="127" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B127" s="2"/>
+      <c r="B127" s="5"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="2"/>
     </row>
     <row r="128" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B128" s="2"/>
+      <c r="B128" s="5"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="2"/>
     </row>
     <row r="129" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B129" s="2"/>
+      <c r="B129" s="5"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="2"/>
     </row>
     <row r="130" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B130" s="2"/>
+      <c r="B130" s="5"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="2"/>
     </row>
     <row r="131" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B131" s="2"/>
+      <c r="B131" s="5"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="2"/>
     </row>
     <row r="132" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B132" s="2"/>
+      <c r="B132" s="5"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="2"/>
     </row>
     <row r="133" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B133" s="2"/>
+      <c r="B133" s="5"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="2"/>
     </row>
     <row r="134" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B134" s="2"/>
+      <c r="B134" s="5"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="2"/>
     </row>
     <row r="135" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B135" s="2"/>
+      <c r="B135" s="5"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="2"/>
     </row>
     <row r="136" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B136" s="2"/>
+      <c r="B136" s="5"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="2"/>
     </row>
     <row r="137" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B137" s="2"/>
+      <c r="B137" s="5"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="2"/>
     </row>
     <row r="138" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B138" s="2"/>
+      <c r="B138" s="5"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="2"/>
     </row>
     <row r="139" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B139" s="2"/>
+      <c r="B139" s="5"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="2"/>
     </row>
     <row r="140" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B140" s="2"/>
+      <c r="B140" s="5"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="2"/>
     </row>
     <row r="141" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B141" s="2"/>
+      <c r="B141" s="5"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="2"/>
     </row>
     <row r="142" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B142" s="2"/>
+      <c r="B142" s="5"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="2"/>
     </row>
     <row r="143" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="2"/>
+      <c r="B143" s="5"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="2"/>
     </row>
     <row r="144" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B144" s="2"/>
+      <c r="B144" s="5"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="2"/>
     </row>
     <row r="145" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B145" s="2"/>
+      <c r="B145" s="5"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="2"/>
     </row>
     <row r="146" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="2"/>
+      <c r="B146" s="5"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="2"/>
     </row>
     <row r="147" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="2"/>
+      <c r="B147" s="5"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="2"/>
     </row>
     <row r="148" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B148" s="2"/>
+      <c r="B148" s="5"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="2"/>
     </row>
     <row r="149" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="2"/>
+      <c r="B149" s="5"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="2"/>
     </row>
     <row r="150" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B150" s="2"/>
+      <c r="B150" s="5"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="2"/>
     </row>
     <row r="151" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B151" s="2"/>
+      <c r="B151" s="5"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="2"/>
     </row>
     <row r="152" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="2"/>
+      <c r="B152" s="5"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="2"/>
     </row>
     <row r="153" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="2"/>
+      <c r="B153" s="5"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="2"/>
     </row>
     <row r="154" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B154" s="2"/>
+      <c r="B154" s="5"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="2"/>
     </row>
     <row r="155" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B155" s="2"/>
+      <c r="B155" s="5"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="2"/>
     </row>
     <row r="156" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B156" s="2"/>
+      <c r="B156" s="5"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="2"/>
     </row>
     <row r="157" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="2"/>
+      <c r="B157" s="5"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="2"/>
     </row>
     <row r="158" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B158" s="2"/>
+      <c r="B158" s="5"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="2"/>
     </row>
     <row r="159" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B159" s="2"/>
+      <c r="B159" s="5"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="2"/>
     </row>
     <row r="160" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B160" s="2"/>
+      <c r="B160" s="5"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="2"/>
     </row>
     <row r="161" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B161" s="2"/>
+      <c r="B161" s="5"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="2"/>
     </row>
     <row r="162" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B162" s="2"/>
+      <c r="B162" s="5"/>
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="2"/>
     </row>
     <row r="163" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B163" s="2"/>
+      <c r="B163" s="5"/>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="2"/>
     </row>
     <row r="164" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B164" s="2"/>
+      <c r="B164" s="5"/>
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="2"/>
     </row>
     <row r="165" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B165" s="2"/>
+      <c r="B165" s="5"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="2"/>
     </row>
     <row r="166" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B166" s="2"/>
+      <c r="B166" s="5"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="2"/>
     </row>
     <row r="167" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B167" s="2"/>
+      <c r="B167" s="5"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="2"/>
     </row>
     <row r="168" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B168" s="2"/>
+      <c r="B168" s="5"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="2"/>
     </row>
     <row r="169" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B169" s="2"/>
+      <c r="B169" s="5"/>
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="2"/>
     </row>
     <row r="170" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B170" s="2"/>
+      <c r="B170" s="5"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="2"/>
     </row>
     <row r="171" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B171" s="2"/>
+      <c r="B171" s="5"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="2"/>
     </row>
     <row r="172" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B172" s="2"/>
+      <c r="B172" s="5"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="2"/>
     </row>
     <row r="173" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B173" s="2"/>
+      <c r="B173" s="5"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="2"/>
     </row>
     <row r="174" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B174" s="2"/>
+      <c r="B174" s="5"/>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="2"/>
     </row>
     <row r="175" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B175" s="2"/>
+      <c r="B175" s="5"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="2"/>
     </row>
     <row r="176" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B176" s="2"/>
+      <c r="B176" s="5"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="2"/>
     </row>
     <row r="177" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B177" s="2"/>
+      <c r="B177" s="5"/>
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="2"/>
     </row>
     <row r="178" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B178" s="2"/>
+      <c r="B178" s="5"/>
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="2"/>
     </row>
     <row r="179" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B179" s="2"/>
+      <c r="B179" s="5"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="2"/>
     </row>
     <row r="180" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B180" s="2"/>
+      <c r="B180" s="5"/>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="2"/>
     </row>
     <row r="181" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B181" s="2"/>
+      <c r="B181" s="5"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="2"/>
     </row>
     <row r="182" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B182" s="2"/>
+      <c r="B182" s="5"/>
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="2"/>
     </row>
     <row r="183" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B183" s="2"/>
+      <c r="B183" s="5"/>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="2"/>
     </row>
     <row r="184" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B184" s="2"/>
+      <c r="B184" s="5"/>
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="2"/>
     </row>
     <row r="185" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B185" s="2"/>
+      <c r="B185" s="5"/>
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="2"/>
     </row>
     <row r="186" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B186" s="2"/>
+      <c r="B186" s="5"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="2"/>
     </row>
     <row r="187" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B187" s="2"/>
+      <c r="B187" s="5"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="2"/>
     </row>
     <row r="188" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B188" s="2"/>
+      <c r="B188" s="5"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="2"/>
     </row>
     <row r="189" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B189" s="2"/>
+      <c r="B189" s="5"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="2"/>
     </row>
     <row r="190" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B190" s="2"/>
+      <c r="B190" s="5"/>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="2"/>
     </row>
     <row r="191" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B191" s="2"/>
+      <c r="B191" s="5"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="2"/>
     </row>
     <row r="192" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B192" s="2"/>
+      <c r="B192" s="5"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="2"/>
     </row>
     <row r="193" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B193" s="2"/>
+      <c r="B193" s="5"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="2"/>
     </row>
     <row r="194" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B194" s="2"/>
+      <c r="B194" s="5"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="2"/>
     </row>
     <row r="195" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B195" s="2"/>
+      <c r="B195" s="5"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="2"/>
     </row>
     <row r="196" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B196" s="2"/>
+      <c r="B196" s="5"/>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="2"/>
     </row>
     <row r="197" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B197" s="2"/>
+      <c r="B197" s="5"/>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="2"/>
     </row>
     <row r="198" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B198" s="2"/>
+      <c r="B198" s="5"/>
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="2"/>
     </row>
     <row r="199" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B199" s="2"/>
+      <c r="B199" s="5"/>
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="2"/>
     </row>
     <row r="200" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B200" s="2"/>
+      <c r="B200" s="5"/>
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="2"/>
     </row>
     <row r="201" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B201" s="2"/>
+      <c r="B201" s="5"/>
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="2"/>
     </row>
     <row r="202" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B202" s="2"/>
+      <c r="B202" s="5"/>
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="2"/>
     </row>
     <row r="203" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B203" s="2"/>
+      <c r="B203" s="5"/>
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="2"/>
     </row>
     <row r="204" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B204" s="2"/>
+      <c r="B204" s="5"/>
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="2"/>
     </row>
     <row r="205" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B205" s="2"/>
+      <c r="B205" s="5"/>
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="2"/>
     </row>
     <row r="206" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B206" s="2"/>
+      <c r="B206" s="5"/>
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="2"/>
     </row>
     <row r="207" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B207" s="2"/>
+      <c r="B207" s="5"/>
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="2"/>
     </row>
     <row r="208" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B208" s="2"/>
+      <c r="B208" s="5"/>
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="2"/>
     </row>
     <row r="209" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B209" s="2"/>
+      <c r="B209" s="5"/>
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="2"/>
     </row>
     <row r="210" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B210" s="2"/>
+      <c r="B210" s="5"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="2"/>
     </row>
     <row r="211" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B211" s="2"/>
+      <c r="B211" s="5"/>
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="2"/>
     </row>
     <row r="212" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B212" s="2"/>
+      <c r="B212" s="5"/>
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="2"/>
     </row>
     <row r="213" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B213" s="2"/>
+      <c r="B213" s="5"/>
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="2"/>
     </row>
     <row r="214" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B214" s="2"/>
+      <c r="B214" s="5"/>
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="2"/>
     </row>
     <row r="215" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B215" s="2"/>
+      <c r="B215" s="5"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="2"/>
     </row>
     <row r="216" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B216" s="2"/>
+      <c r="B216" s="5"/>
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="2"/>
     </row>
     <row r="217" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B217" s="2"/>
+      <c r="B217" s="5"/>
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="2"/>
     </row>
     <row r="218" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B218" s="2"/>
+      <c r="B218" s="5"/>
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="2"/>
     </row>
     <row r="219" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B219" s="2"/>
+      <c r="B219" s="5"/>
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="2"/>
     </row>
     <row r="220" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B220" s="2"/>
+      <c r="B220" s="5"/>
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="2"/>
     </row>
     <row r="221" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B221" s="2"/>
+      <c r="B221" s="5"/>
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="2"/>
     </row>
     <row r="222" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B222" s="2"/>
+      <c r="B222" s="5"/>
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="2"/>
     </row>
     <row r="223" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B223" s="2"/>
+      <c r="B223" s="5"/>
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="2"/>
     </row>
     <row r="224" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B224" s="2"/>
+      <c r="B224" s="5"/>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="2"/>
     </row>
     <row r="225" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B225" s="2"/>
+      <c r="B225" s="5"/>
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="2"/>
     </row>
     <row r="226" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B226" s="2"/>
+      <c r="B226" s="5"/>
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="2"/>
     </row>
     <row r="227" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B227" s="2"/>
+      <c r="B227" s="5"/>
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="2"/>
     </row>
     <row r="228" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B228" s="2"/>
+      <c r="B228" s="5"/>
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="2"/>
     </row>
     <row r="229" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B229" s="2"/>
+      <c r="B229" s="5"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="2"/>
     </row>
     <row r="230" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B230" s="2"/>
+      <c r="B230" s="5"/>
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="2"/>
     </row>
     <row r="231" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B231" s="2"/>
+      <c r="B231" s="5"/>
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="2"/>
     </row>
     <row r="232" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B232" s="2"/>
+      <c r="B232" s="5"/>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="2"/>
     </row>
     <row r="233" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B233" s="2"/>
+      <c r="B233" s="5"/>
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="2"/>
     </row>
     <row r="234" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B234" s="2"/>
+      <c r="B234" s="5"/>
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="2"/>
     </row>
     <row r="235" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B235" s="2"/>
+      <c r="B235" s="5"/>
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="2"/>
     </row>
     <row r="236" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B236" s="2"/>
+      <c r="B236" s="5"/>
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="2"/>
     </row>
     <row r="237" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B237" s="2"/>
+      <c r="B237" s="5"/>
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="2"/>
     </row>
     <row r="238" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B238" s="2"/>
+      <c r="B238" s="5"/>
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="2"/>
     </row>
     <row r="239" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B239" s="2"/>
+      <c r="B239" s="5"/>
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="2"/>
     </row>
     <row r="240" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B240" s="2"/>
+      <c r="B240" s="5"/>
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="2"/>
     </row>
     <row r="241" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B241" s="2"/>
+      <c r="B241" s="5"/>
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="2"/>
     </row>
     <row r="242" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B242" s="2"/>
+      <c r="B242" s="5"/>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="2"/>
     </row>
     <row r="243" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B243" s="2"/>
+      <c r="B243" s="5"/>
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="2"/>
     </row>
     <row r="244" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B244" s="2"/>
+      <c r="B244" s="5"/>
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="2"/>
     </row>
     <row r="245" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B245" s="2"/>
+      <c r="B245" s="5"/>
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="2"/>
     </row>
     <row r="246" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B246" s="2"/>
+      <c r="B246" s="5"/>
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="2"/>
     </row>
     <row r="247" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B247" s="2"/>
+      <c r="B247" s="5"/>
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="2"/>
     </row>
     <row r="248" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B248" s="2"/>
+      <c r="B248" s="5"/>
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="2"/>
     </row>
     <row r="249" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B249" s="2"/>
+      <c r="B249" s="5"/>
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="2"/>
     </row>
     <row r="250" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B250" s="2"/>
+      <c r="B250" s="5"/>
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="2"/>
     </row>
     <row r="251" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B251" s="2"/>
+      <c r="B251" s="5"/>
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="2"/>
     </row>
     <row r="252" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B252" s="2"/>
+      <c r="B252" s="5"/>
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="2"/>
     </row>
     <row r="253" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B253" s="2"/>
+      <c r="B253" s="5"/>
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="2"/>
     </row>
     <row r="254" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B254" s="2"/>
+      <c r="B254" s="5"/>
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="2"/>
     </row>
     <row r="255" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B255" s="2"/>
+      <c r="B255" s="5"/>
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="2"/>
     </row>
     <row r="256" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B256" s="2"/>
+      <c r="B256" s="5"/>
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="2"/>
     </row>
     <row r="257" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B257" s="2"/>
+      <c r="B257" s="5"/>
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="2"/>
     </row>
     <row r="258" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B258" s="2"/>
+      <c r="B258" s="5"/>
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="2"/>
     </row>
     <row r="259" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B259" s="2"/>
+      <c r="B259" s="5"/>
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="2"/>
     </row>
     <row r="260" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B260" s="2"/>
+      <c r="B260" s="5"/>
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="2"/>
     </row>
     <row r="261" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B261" s="2"/>
+      <c r="B261" s="5"/>
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="2"/>
     </row>
     <row r="262" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B262" s="2"/>
+      <c r="B262" s="5"/>
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="2"/>
     </row>
     <row r="263" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B263" s="2"/>
+      <c r="B263" s="5"/>
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="2"/>
     </row>
     <row r="264" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B264" s="2"/>
+      <c r="B264" s="5"/>
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="2"/>
     </row>
     <row r="265" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B265" s="2"/>
+      <c r="B265" s="5"/>
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="2"/>
     </row>
     <row r="266" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B266" s="2"/>
+      <c r="B266" s="5"/>
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="2"/>
     </row>
     <row r="267" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B267" s="2"/>
+      <c r="B267" s="5"/>
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="2"/>
     </row>
     <row r="268" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B268" s="2"/>
+      <c r="B268" s="5"/>
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="2"/>
     </row>
     <row r="269" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B269" s="2"/>
+      <c r="B269" s="5"/>
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="2"/>
     </row>
     <row r="270" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B270" s="2"/>
+      <c r="B270" s="5"/>
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="2"/>
     </row>
     <row r="271" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B271" s="2"/>
+      <c r="B271" s="5"/>
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="2"/>
     </row>
     <row r="272" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B272" s="2"/>
+      <c r="B272" s="5"/>
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="2"/>
     </row>
     <row r="273" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B273" s="2"/>
+      <c r="B273" s="5"/>
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="2"/>
     </row>
     <row r="274" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B274" s="2"/>
+      <c r="B274" s="5"/>
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="2"/>
     </row>
     <row r="275" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B275" s="2"/>
+      <c r="B275" s="5"/>
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="2"/>
     </row>
     <row r="276" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B276" s="2"/>
+      <c r="B276" s="5"/>
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="2"/>
     </row>
     <row r="277" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B277" s="2"/>
+      <c r="B277" s="5"/>
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="2"/>
     </row>
     <row r="278" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B278" s="2"/>
+      <c r="B278" s="5"/>
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="2"/>
     </row>
     <row r="279" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B279" s="2"/>
+      <c r="B279" s="5"/>
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="2"/>
     </row>
     <row r="280" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B280" s="2"/>
+      <c r="B280" s="5"/>
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="2"/>
     </row>
     <row r="281" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B281" s="2"/>
+      <c r="B281" s="5"/>
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="2"/>
     </row>
     <row r="282" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B282" s="2"/>
+      <c r="B282" s="5"/>
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="2"/>
     </row>
     <row r="283" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B283" s="2"/>
+      <c r="B283" s="5"/>
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="2"/>
     </row>
     <row r="284" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B284" s="2"/>
+      <c r="B284" s="5"/>
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="2"/>
     </row>
     <row r="285" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B285" s="2"/>
+      <c r="B285" s="5"/>
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="2"/>
     </row>
     <row r="286" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B286" s="2"/>
+      <c r="B286" s="5"/>
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="2"/>
     </row>
     <row r="287" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B287" s="2"/>
+      <c r="B287" s="5"/>
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="2"/>
     </row>
     <row r="288" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B288" s="2"/>
+      <c r="B288" s="5"/>
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="2"/>
     </row>
     <row r="289" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B289" s="2"/>
+      <c r="B289" s="5"/>
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="2"/>
     </row>
     <row r="290" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B290" s="2"/>
+      <c r="B290" s="5"/>
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="2"/>
     </row>
     <row r="291" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B291" s="2"/>
+      <c r="B291" s="5"/>
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="2"/>
     </row>
     <row r="292" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B292" s="2"/>
+      <c r="B292" s="5"/>
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="2"/>
@@ -2595,7 +2614,7 @@
         <v>47</v>
       </c>
       <c r="J1" s="2"/>
-      <c r="K1" s="16"/>
+      <c r="K1" s="15"/>
       <c r="L1" s="2" t="s">
         <v>48</v>
       </c>

--- a/Documentos/Outros/BES3543 - Status Comissionamento.xlsx
+++ b/Documentos/Outros/BES3543 - Status Comissionamento.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180"/>
+    <workbookView windowWidth="27945" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="Pendencias " sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="55">
   <si>
     <t>Pendencias</t>
   </si>
@@ -69,28 +69,34 @@
     <t>OK</t>
   </si>
   <si>
+    <t>28/set</t>
+  </si>
+  <si>
     <t>Validação de Tela de Contagem e Dados</t>
   </si>
   <si>
+    <t>30/set</t>
+  </si>
+  <si>
+    <t>Separação de Botões de Comando Porta e Botoeira Central</t>
+  </si>
+  <si>
+    <t>Teste de ciclo real para função de Inspeção</t>
+  </si>
+  <si>
+    <t>Inserir numero de Inspeções na IHM</t>
+  </si>
+  <si>
+    <t>Inserir comando para fazer inspeção no próximo ciclo</t>
+  </si>
+  <si>
+    <t>Fazer intertravamento para que o ciclo só comece após término de todos os Homes</t>
+  </si>
+  <si>
+    <t>Testar Etiquetadora</t>
+  </si>
+  <si>
     <t>ni</t>
-  </si>
-  <si>
-    <t>Separação de Botões de Comando Porta e Botoeira Central</t>
-  </si>
-  <si>
-    <t>Teste de ciclo real para função de Inspeção</t>
-  </si>
-  <si>
-    <t>Inserir numero de Inspeções na IHM</t>
-  </si>
-  <si>
-    <t>Inserir comando para fazer inspeção no próximo ciclo</t>
-  </si>
-  <si>
-    <t>Fazer intertravamento para que o ciclo só comece após término de todos os Homes</t>
-  </si>
-  <si>
-    <t>Testar Etiquetadora</t>
   </si>
   <si>
     <t>Colocar na IHM o campo para editar Posição de Corte do Giro do Envolvedor</t>
@@ -1288,7 +1294,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:E293"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="82.4416666666667" style="15" customWidth="1"/>
@@ -1297,8 +1303,8 @@
     <col min="5" max="5" width="62.2166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15" spans="2:5">
+    <row r="1" ht="15"/>
+    <row r="2" ht="16.5" spans="2:5">
       <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
@@ -1312,7 +1318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="2:5">
+    <row r="3" ht="15.75" spans="2:5">
       <c r="B3" s="11" t="s">
         <v>4</v>
       </c>
@@ -1324,7 +1330,7 @@
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" ht="15" spans="2:5">
+    <row r="4" ht="15.75" spans="2:5">
       <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
@@ -1336,7 +1342,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" ht="15" spans="2:5">
+    <row r="5" ht="15.75" spans="2:5">
       <c r="B5" s="11" t="s">
         <v>7</v>
       </c>
@@ -1346,7 +1352,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" ht="15" spans="2:5">
+    <row r="6" ht="15.75" spans="2:5">
       <c r="B6" s="11" t="s">
         <v>9</v>
       </c>
@@ -1358,7 +1364,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" ht="15" spans="2:5">
+    <row r="7" ht="15.75" spans="2:5">
       <c r="B7" s="11" t="s">
         <v>10</v>
       </c>
@@ -1370,39 +1376,43 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="2:5">
+    <row r="8" ht="15.75" spans="2:5">
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" ht="15" spans="2:5">
+    <row r="9" ht="15.75" spans="2:5">
       <c r="B9" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="7"/>
+        <v>5</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" ht="15" spans="2:5">
+    <row r="10" ht="15.75" spans="2:5">
       <c r="B10" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" ht="15" spans="2:5">
+    <row r="11" ht="15.75" spans="2:5">
       <c r="B11" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>5</v>
@@ -1412,1717 +1422,1725 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" ht="15.75" spans="2:5">
       <c r="B12" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" ht="15.75" spans="2:5">
       <c r="B13" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="2:5">
+    <row r="14" ht="15.75" spans="2:5">
       <c r="B14" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" ht="15" spans="2:5">
+    <row r="15" ht="15.75" spans="2:5">
       <c r="B15" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" ht="15.75" spans="2:5">
       <c r="B16" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="7"/>
+      <c r="D16" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" ht="15" spans="2:5">
+    <row r="17" ht="15.75" spans="2:5">
       <c r="B17" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" ht="15" spans="2:5">
+    <row r="18" ht="15.75" spans="2:5">
       <c r="B18" s="11"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" ht="15" spans="2:5">
+    <row r="19" ht="15.75" spans="2:5">
       <c r="B19" s="11"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" ht="15" spans="2:5">
+    <row r="20" ht="15.75" spans="2:5">
       <c r="B20" s="11"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" ht="15" spans="2:5">
+    <row r="21" ht="15.75" spans="2:5">
       <c r="B21" s="11"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" ht="15" spans="2:5">
+    <row r="22" ht="15.75" spans="2:5">
       <c r="B22" s="11"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" ht="15" spans="2:5">
+    <row r="23" ht="15.75" spans="2:5">
       <c r="B23" s="11"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" ht="15" spans="2:5">
+    <row r="24" ht="15.75" spans="2:5">
       <c r="B24" s="11"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" ht="15" spans="2:5">
+    <row r="25" ht="15.75" spans="2:5">
       <c r="B25" s="11"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" ht="15" spans="2:5">
+    <row r="26" ht="15.75" spans="2:5">
       <c r="B26" s="11"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" ht="15" spans="2:5">
+    <row r="27" ht="15.75" spans="2:5">
       <c r="B27" s="11"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" ht="15" spans="2:5">
+    <row r="28" ht="15.75" spans="2:5">
       <c r="B28" s="11"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" ht="15" spans="2:5">
+    <row r="29" ht="15.75" spans="2:5">
       <c r="B29" s="11"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" ht="15" spans="2:5">
+    <row r="30" ht="15.75" spans="2:5">
       <c r="B30" s="11"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" ht="15" spans="2:5">
+    <row r="31" ht="15.75" spans="2:5">
       <c r="B31" s="11"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" ht="15" spans="2:5">
+    <row r="32" ht="15.75" spans="2:5">
       <c r="B32" s="11"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" ht="15" spans="2:5">
+    <row r="33" ht="15.75" spans="2:5">
       <c r="B33" s="11"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" ht="15" spans="2:5">
+    <row r="34" ht="15.75" spans="2:5">
       <c r="B34" s="11"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" ht="15" spans="2:5">
+    <row r="35" ht="15.75" spans="2:5">
       <c r="B35" s="11"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" ht="15" spans="2:5">
+    <row r="36" ht="15.75" spans="2:5">
       <c r="B36" s="11"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" ht="15" spans="2:5">
+    <row r="37" ht="15.75" spans="2:5">
       <c r="B37" s="11"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" ht="15" spans="2:5">
+    <row r="38" ht="15.75" spans="2:5">
       <c r="B38" s="11"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" ht="15" spans="2:5">
+    <row r="39" ht="15.75" spans="2:5">
       <c r="B39" s="11"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="2"/>
     </row>
-    <row r="40" ht="15" spans="2:5">
+    <row r="40" ht="15.75" spans="2:5">
       <c r="B40" s="11"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" ht="15" spans="2:5">
+    <row r="41" ht="15.75" spans="2:5">
       <c r="B41" s="11"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" ht="15" spans="2:5">
+    <row r="42" ht="15.75" spans="2:5">
       <c r="B42" s="11"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" ht="15" spans="2:5">
+    <row r="43" ht="15.75" spans="2:5">
       <c r="B43" s="11"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" ht="15" spans="2:5">
+    <row r="44" ht="15.75" spans="2:5">
       <c r="B44" s="11"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" ht="15" spans="2:5">
+    <row r="45" ht="15.75" spans="2:5">
       <c r="B45" s="11"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" ht="15" spans="2:5">
+    <row r="46" ht="15.75" spans="2:5">
       <c r="B46" s="11"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" ht="15" spans="2:5">
+    <row r="47" ht="15.75" spans="2:5">
       <c r="B47" s="11"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" ht="15" spans="2:5">
+    <row r="48" ht="15.75" spans="2:5">
       <c r="B48" s="11"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" ht="15" spans="2:5">
+    <row r="49" ht="15.75" spans="2:5">
       <c r="B49" s="11"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" ht="15" spans="2:5">
+    <row r="50" ht="15.75" spans="2:5">
       <c r="B50" s="11"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" ht="15" spans="2:5">
+    <row r="51" ht="15.75" spans="2:5">
       <c r="B51" s="11"/>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="2"/>
     </row>
-    <row r="52" ht="15" spans="2:5">
+    <row r="52" ht="15.75" spans="2:5">
       <c r="B52" s="11"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" ht="15" spans="2:5">
+    <row r="53" ht="15.75" spans="2:5">
       <c r="B53" s="11"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" ht="15" spans="2:5">
+    <row r="54" ht="15.75" spans="2:5">
       <c r="B54" s="11"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" ht="15" spans="2:5">
+    <row r="55" ht="15.75" spans="2:5">
       <c r="B55" s="11"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" ht="15" spans="2:5">
+    <row r="56" ht="15.75" spans="2:5">
       <c r="B56" s="11"/>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" ht="15" spans="2:5">
+    <row r="57" ht="15.75" spans="2:5">
       <c r="B57" s="11"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" ht="15" spans="2:5">
+    <row r="58" ht="15.75" spans="2:5">
       <c r="B58" s="11"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" ht="15" spans="2:5">
+    <row r="59" ht="15.75" spans="2:5">
       <c r="B59" s="11"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" ht="15" spans="2:5">
+    <row r="60" ht="15.75" spans="2:5">
       <c r="B60" s="11"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="2"/>
     </row>
-    <row r="61" ht="15" spans="2:5">
+    <row r="61" ht="15.75" spans="2:5">
       <c r="B61" s="11"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" ht="15" spans="2:5">
+    <row r="62" ht="15.75" spans="2:5">
       <c r="B62" s="11"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" ht="15" spans="2:5">
+    <row r="63" ht="15.75" spans="2:5">
       <c r="B63" s="11"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" ht="15" spans="2:5">
+    <row r="64" ht="15.75" spans="2:5">
       <c r="B64" s="11"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" ht="15" spans="2:5">
+    <row r="65" ht="15.75" spans="2:5">
       <c r="B65" s="11"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" ht="15" spans="2:5">
+    <row r="66" ht="15.75" spans="2:5">
       <c r="B66" s="11"/>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="2"/>
     </row>
-    <row r="67" ht="15" spans="2:5">
+    <row r="67" ht="15.75" spans="2:5">
       <c r="B67" s="11"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
       <c r="E67" s="2"/>
     </row>
-    <row r="68" ht="15" spans="2:5">
+    <row r="68" ht="15.75" spans="2:5">
       <c r="B68" s="11"/>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
       <c r="E68" s="2"/>
     </row>
-    <row r="69" ht="15" spans="2:5">
+    <row r="69" ht="15.75" spans="2:5">
       <c r="B69" s="11"/>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" ht="15" spans="2:5">
+    <row r="70" ht="15.75" spans="2:5">
       <c r="B70" s="11"/>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" ht="15" spans="2:5">
+    <row r="71" ht="15.75" spans="2:5">
       <c r="B71" s="11"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
       <c r="E71" s="2"/>
     </row>
-    <row r="72" ht="15" spans="2:5">
+    <row r="72" ht="15.75" spans="2:5">
       <c r="B72" s="11"/>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" ht="15" spans="2:5">
+    <row r="73" ht="15.75" spans="2:5">
       <c r="B73" s="11"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
       <c r="E73" s="2"/>
     </row>
-    <row r="74" ht="15" spans="2:5">
+    <row r="74" ht="15.75" spans="2:5">
       <c r="B74" s="11"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="E74" s="2"/>
     </row>
-    <row r="75" ht="15" spans="2:5">
+    <row r="75" ht="15.75" spans="2:5">
       <c r="B75" s="11"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" ht="15" spans="2:5">
+    <row r="76" ht="15.75" spans="2:5">
       <c r="B76" s="11"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" ht="15" spans="2:5">
+    <row r="77" ht="15.75" spans="2:5">
       <c r="B77" s="11"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" ht="15" spans="2:5">
+    <row r="78" ht="15.75" spans="2:5">
       <c r="B78" s="11"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" ht="15" spans="2:5">
+    <row r="79" ht="15.75" spans="2:5">
       <c r="B79" s="11"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" ht="15" spans="2:5">
+    <row r="80" ht="15.75" spans="2:5">
       <c r="B80" s="11"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" ht="15" spans="2:5">
+    <row r="81" ht="15.75" spans="2:5">
       <c r="B81" s="11"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" ht="15" spans="2:5">
+    <row r="82" ht="15.75" spans="2:5">
       <c r="B82" s="11"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" ht="15" spans="2:5">
+    <row r="83" ht="15.75" spans="2:5">
       <c r="B83" s="11"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" ht="15" spans="2:5">
+    <row r="84" ht="15.75" spans="2:5">
       <c r="B84" s="11"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" ht="15" spans="2:5">
+    <row r="85" ht="15.75" spans="2:5">
       <c r="B85" s="11"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="E85" s="2"/>
     </row>
-    <row r="86" ht="15" spans="2:5">
+    <row r="86" ht="15.75" spans="2:5">
       <c r="B86" s="11"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="2"/>
     </row>
-    <row r="87" ht="15" spans="2:5">
+    <row r="87" ht="15.75" spans="2:5">
       <c r="B87" s="11"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="2"/>
     </row>
-    <row r="88" ht="15" spans="2:5">
+    <row r="88" ht="15.75" spans="2:5">
       <c r="B88" s="11"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" ht="15" spans="2:5">
+    <row r="89" ht="15.75" spans="2:5">
       <c r="B89" s="11"/>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" ht="15" spans="2:5">
+    <row r="90" ht="15.75" spans="2:5">
       <c r="B90" s="11"/>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" ht="15" spans="2:5">
+    <row r="91" ht="15.75" spans="2:5">
       <c r="B91" s="11"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
       <c r="E91" s="2"/>
     </row>
-    <row r="92" ht="15" spans="2:5">
+    <row r="92" ht="15.75" spans="2:5">
       <c r="B92" s="11"/>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
       <c r="E92" s="2"/>
     </row>
-    <row r="93" ht="15" spans="2:5">
+    <row r="93" ht="15.75" spans="2:5">
       <c r="B93" s="11"/>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="2"/>
     </row>
-    <row r="94" ht="15" spans="2:5">
+    <row r="94" ht="15.75" spans="2:5">
       <c r="B94" s="11"/>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" ht="15" spans="2:5">
+    <row r="95" ht="15.75" spans="2:5">
       <c r="B95" s="11"/>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
       <c r="E95" s="2"/>
     </row>
-    <row r="96" ht="15" spans="2:5">
+    <row r="96" ht="15.75" spans="2:5">
       <c r="B96" s="11"/>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" ht="15" spans="2:5">
+    <row r="97" ht="15.75" spans="2:5">
       <c r="B97" s="11"/>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" ht="15" spans="2:5">
+    <row r="98" ht="15.75" spans="2:5">
       <c r="B98" s="11"/>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
       <c r="E98" s="2"/>
     </row>
-    <row r="99" ht="15" spans="2:5">
+    <row r="99" ht="15.75" spans="2:5">
       <c r="B99" s="11"/>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" ht="15" spans="2:5">
+    <row r="100" ht="15.75" spans="2:5">
       <c r="B100" s="11"/>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" ht="15" spans="2:5">
+    <row r="101" ht="15.75" spans="2:5">
       <c r="B101" s="11"/>
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
       <c r="E101" s="2"/>
     </row>
-    <row r="102" ht="15" spans="2:5">
+    <row r="102" ht="15.75" spans="2:5">
       <c r="B102" s="11"/>
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" ht="15" spans="2:5">
+    <row r="103" ht="15.75" spans="2:5">
       <c r="B103" s="11"/>
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" ht="15" spans="2:5">
+    <row r="104" ht="15.75" spans="2:5">
       <c r="B104" s="11"/>
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" ht="15" spans="2:5">
+    <row r="105" ht="15.75" spans="2:5">
       <c r="B105" s="11"/>
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" ht="15" spans="2:5">
+    <row r="106" ht="15.75" spans="2:5">
       <c r="B106" s="11"/>
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" ht="15" spans="2:5">
+    <row r="107" ht="15.75" spans="2:5">
       <c r="B107" s="11"/>
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
       <c r="E107" s="2"/>
     </row>
-    <row r="108" ht="15" spans="2:5">
+    <row r="108" ht="15.75" spans="2:5">
       <c r="B108" s="11"/>
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
       <c r="E108" s="2"/>
     </row>
-    <row r="109" ht="15" spans="2:5">
+    <row r="109" ht="15.75" spans="2:5">
       <c r="B109" s="11"/>
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
       <c r="E109" s="2"/>
     </row>
-    <row r="110" ht="15" spans="2:5">
+    <row r="110" ht="15.75" spans="2:5">
       <c r="B110" s="11"/>
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
       <c r="E110" s="2"/>
     </row>
-    <row r="111" ht="15" spans="2:5">
+    <row r="111" ht="15.75" spans="2:5">
       <c r="B111" s="11"/>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
       <c r="E111" s="2"/>
     </row>
-    <row r="112" ht="15" spans="2:5">
+    <row r="112" ht="15.75" spans="2:5">
       <c r="B112" s="11"/>
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
       <c r="E112" s="2"/>
     </row>
-    <row r="113" ht="15" spans="2:5">
+    <row r="113" ht="15.75" spans="2:5">
       <c r="B113" s="11"/>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
       <c r="E113" s="2"/>
     </row>
-    <row r="114" ht="15" spans="2:5">
+    <row r="114" ht="15.75" spans="2:5">
       <c r="B114" s="11"/>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
       <c r="E114" s="2"/>
     </row>
-    <row r="115" ht="15" spans="2:5">
+    <row r="115" ht="15.75" spans="2:5">
       <c r="B115" s="11"/>
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
       <c r="E115" s="2"/>
     </row>
-    <row r="116" ht="15" spans="2:5">
+    <row r="116" ht="15.75" spans="2:5">
       <c r="B116" s="11"/>
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
       <c r="E116" s="2"/>
     </row>
-    <row r="117" ht="15" spans="2:5">
+    <row r="117" ht="15.75" spans="2:5">
       <c r="B117" s="11"/>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
       <c r="E117" s="2"/>
     </row>
-    <row r="118" ht="15" spans="2:5">
+    <row r="118" ht="15.75" spans="2:5">
       <c r="B118" s="11"/>
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
       <c r="E118" s="2"/>
     </row>
-    <row r="119" ht="15" spans="2:5">
+    <row r="119" ht="15.75" spans="2:5">
       <c r="B119" s="11"/>
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
       <c r="E119" s="2"/>
     </row>
-    <row r="120" ht="15" spans="2:5">
+    <row r="120" ht="15.75" spans="2:5">
       <c r="B120" s="11"/>
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
       <c r="E120" s="2"/>
     </row>
-    <row r="121" ht="15" spans="2:5">
+    <row r="121" ht="15.75" spans="2:5">
       <c r="B121" s="11"/>
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
       <c r="E121" s="2"/>
     </row>
-    <row r="122" ht="15" spans="2:5">
+    <row r="122" ht="15.75" spans="2:5">
       <c r="B122" s="11"/>
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
       <c r="E122" s="2"/>
     </row>
-    <row r="123" ht="15" spans="2:5">
+    <row r="123" ht="15.75" spans="2:5">
       <c r="B123" s="11"/>
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
       <c r="E123" s="2"/>
     </row>
-    <row r="124" ht="15" spans="2:5">
+    <row r="124" ht="15.75" spans="2:5">
       <c r="B124" s="11"/>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
       <c r="E124" s="2"/>
     </row>
-    <row r="125" ht="15" spans="2:5">
+    <row r="125" ht="15.75" spans="2:5">
       <c r="B125" s="11"/>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
       <c r="E125" s="2"/>
     </row>
-    <row r="126" ht="15" spans="2:5">
+    <row r="126" ht="15.75" spans="2:5">
       <c r="B126" s="11"/>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
       <c r="E126" s="2"/>
     </row>
-    <row r="127" ht="15" spans="2:5">
+    <row r="127" ht="15.75" spans="2:5">
       <c r="B127" s="11"/>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
       <c r="E127" s="2"/>
     </row>
-    <row r="128" ht="15" spans="2:5">
+    <row r="128" ht="15.75" spans="2:5">
       <c r="B128" s="11"/>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
       <c r="E128" s="2"/>
     </row>
-    <row r="129" ht="15" spans="2:5">
+    <row r="129" ht="15.75" spans="2:5">
       <c r="B129" s="11"/>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
       <c r="E129" s="2"/>
     </row>
-    <row r="130" ht="15" spans="2:5">
+    <row r="130" ht="15.75" spans="2:5">
       <c r="B130" s="11"/>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
       <c r="E130" s="2"/>
     </row>
-    <row r="131" ht="15" spans="2:5">
+    <row r="131" ht="15.75" spans="2:5">
       <c r="B131" s="11"/>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
       <c r="E131" s="2"/>
     </row>
-    <row r="132" ht="15" spans="2:5">
+    <row r="132" ht="15.75" spans="2:5">
       <c r="B132" s="11"/>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
       <c r="E132" s="2"/>
     </row>
-    <row r="133" ht="15" spans="2:5">
+    <row r="133" ht="15.75" spans="2:5">
       <c r="B133" s="11"/>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
       <c r="E133" s="2"/>
     </row>
-    <row r="134" ht="15" spans="2:5">
+    <row r="134" ht="15.75" spans="2:5">
       <c r="B134" s="11"/>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
       <c r="E134" s="2"/>
     </row>
-    <row r="135" ht="15" spans="2:5">
+    <row r="135" ht="15.75" spans="2:5">
       <c r="B135" s="11"/>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
       <c r="E135" s="2"/>
     </row>
-    <row r="136" ht="15" spans="2:5">
+    <row r="136" ht="15.75" spans="2:5">
       <c r="B136" s="11"/>
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
       <c r="E136" s="2"/>
     </row>
-    <row r="137" ht="15" spans="2:5">
+    <row r="137" ht="15.75" spans="2:5">
       <c r="B137" s="11"/>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
       <c r="E137" s="2"/>
     </row>
-    <row r="138" ht="15" spans="2:5">
+    <row r="138" ht="15.75" spans="2:5">
       <c r="B138" s="11"/>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
       <c r="E138" s="2"/>
     </row>
-    <row r="139" ht="15" spans="2:5">
+    <row r="139" ht="15.75" spans="2:5">
       <c r="B139" s="11"/>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
       <c r="E139" s="2"/>
     </row>
-    <row r="140" ht="15" spans="2:5">
+    <row r="140" ht="15.75" spans="2:5">
       <c r="B140" s="11"/>
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
       <c r="E140" s="2"/>
     </row>
-    <row r="141" ht="15" spans="2:5">
+    <row r="141" ht="15.75" spans="2:5">
       <c r="B141" s="11"/>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
       <c r="E141" s="2"/>
     </row>
-    <row r="142" ht="15" spans="2:5">
+    <row r="142" ht="15.75" spans="2:5">
       <c r="B142" s="11"/>
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
       <c r="E142" s="2"/>
     </row>
-    <row r="143" ht="15" spans="2:5">
+    <row r="143" ht="15.75" spans="2:5">
       <c r="B143" s="11"/>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
       <c r="E143" s="2"/>
     </row>
-    <row r="144" ht="15" spans="2:5">
+    <row r="144" ht="15.75" spans="2:5">
       <c r="B144" s="11"/>
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
       <c r="E144" s="2"/>
     </row>
-    <row r="145" ht="15" spans="2:5">
+    <row r="145" ht="15.75" spans="2:5">
       <c r="B145" s="11"/>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
       <c r="E145" s="2"/>
     </row>
-    <row r="146" ht="15" spans="2:5">
+    <row r="146" ht="15.75" spans="2:5">
       <c r="B146" s="11"/>
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
       <c r="E146" s="2"/>
     </row>
-    <row r="147" ht="15" spans="2:5">
+    <row r="147" ht="15.75" spans="2:5">
       <c r="B147" s="11"/>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
       <c r="E147" s="2"/>
     </row>
-    <row r="148" ht="15" spans="2:5">
+    <row r="148" ht="15.75" spans="2:5">
       <c r="B148" s="11"/>
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
       <c r="E148" s="2"/>
     </row>
-    <row r="149" ht="15" spans="2:5">
+    <row r="149" ht="15.75" spans="2:5">
       <c r="B149" s="11"/>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
       <c r="E149" s="2"/>
     </row>
-    <row r="150" ht="15" spans="2:5">
+    <row r="150" ht="15.75" spans="2:5">
       <c r="B150" s="11"/>
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
       <c r="E150" s="2"/>
     </row>
-    <row r="151" ht="15" spans="2:5">
+    <row r="151" ht="15.75" spans="2:5">
       <c r="B151" s="11"/>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
       <c r="E151" s="2"/>
     </row>
-    <row r="152" ht="15" spans="2:5">
+    <row r="152" ht="15.75" spans="2:5">
       <c r="B152" s="11"/>
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
       <c r="E152" s="2"/>
     </row>
-    <row r="153" ht="15" spans="2:5">
+    <row r="153" ht="15.75" spans="2:5">
       <c r="B153" s="11"/>
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
       <c r="E153" s="2"/>
     </row>
-    <row r="154" ht="15" spans="2:5">
+    <row r="154" ht="15.75" spans="2:5">
       <c r="B154" s="11"/>
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
       <c r="E154" s="2"/>
     </row>
-    <row r="155" ht="15" spans="2:5">
+    <row r="155" ht="15.75" spans="2:5">
       <c r="B155" s="11"/>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
       <c r="E155" s="2"/>
     </row>
-    <row r="156" ht="15" spans="2:5">
+    <row r="156" ht="15.75" spans="2:5">
       <c r="B156" s="11"/>
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
       <c r="E156" s="2"/>
     </row>
-    <row r="157" ht="15" spans="2:5">
+    <row r="157" ht="15.75" spans="2:5">
       <c r="B157" s="11"/>
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
       <c r="E157" s="2"/>
     </row>
-    <row r="158" ht="15" spans="2:5">
+    <row r="158" ht="15.75" spans="2:5">
       <c r="B158" s="11"/>
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
       <c r="E158" s="2"/>
     </row>
-    <row r="159" ht="15" spans="2:5">
+    <row r="159" ht="15.75" spans="2:5">
       <c r="B159" s="11"/>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
       <c r="E159" s="2"/>
     </row>
-    <row r="160" ht="15" spans="2:5">
+    <row r="160" ht="15.75" spans="2:5">
       <c r="B160" s="11"/>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
       <c r="E160" s="2"/>
     </row>
-    <row r="161" ht="15" spans="2:5">
+    <row r="161" ht="15.75" spans="2:5">
       <c r="B161" s="11"/>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
       <c r="E161" s="2"/>
     </row>
-    <row r="162" ht="15" spans="2:5">
+    <row r="162" ht="15.75" spans="2:5">
       <c r="B162" s="11"/>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
       <c r="E162" s="2"/>
     </row>
-    <row r="163" ht="15" spans="2:5">
+    <row r="163" ht="15.75" spans="2:5">
       <c r="B163" s="11"/>
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
       <c r="E163" s="2"/>
     </row>
-    <row r="164" ht="15" spans="2:5">
+    <row r="164" ht="15.75" spans="2:5">
       <c r="B164" s="11"/>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
       <c r="E164" s="2"/>
     </row>
-    <row r="165" ht="15" spans="2:5">
+    <row r="165" ht="15.75" spans="2:5">
       <c r="B165" s="11"/>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
       <c r="E165" s="2"/>
     </row>
-    <row r="166" ht="15" spans="2:5">
+    <row r="166" ht="15.75" spans="2:5">
       <c r="B166" s="11"/>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
       <c r="E166" s="2"/>
     </row>
-    <row r="167" ht="15" spans="2:5">
+    <row r="167" ht="15.75" spans="2:5">
       <c r="B167" s="11"/>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
       <c r="E167" s="2"/>
     </row>
-    <row r="168" ht="15" spans="2:5">
+    <row r="168" ht="15.75" spans="2:5">
       <c r="B168" s="11"/>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
       <c r="E168" s="2"/>
     </row>
-    <row r="169" ht="15" spans="2:5">
+    <row r="169" ht="15.75" spans="2:5">
       <c r="B169" s="11"/>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
       <c r="E169" s="2"/>
     </row>
-    <row r="170" ht="15" spans="2:5">
+    <row r="170" ht="15.75" spans="2:5">
       <c r="B170" s="11"/>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
       <c r="E170" s="2"/>
     </row>
-    <row r="171" ht="15" spans="2:5">
+    <row r="171" ht="15.75" spans="2:5">
       <c r="B171" s="11"/>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
       <c r="E171" s="2"/>
     </row>
-    <row r="172" ht="15" spans="2:5">
+    <row r="172" ht="15.75" spans="2:5">
       <c r="B172" s="11"/>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
       <c r="E172" s="2"/>
     </row>
-    <row r="173" ht="15" spans="2:5">
+    <row r="173" ht="15.75" spans="2:5">
       <c r="B173" s="11"/>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
       <c r="E173" s="2"/>
     </row>
-    <row r="174" ht="15" spans="2:5">
+    <row r="174" ht="15.75" spans="2:5">
       <c r="B174" s="11"/>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
       <c r="E174" s="2"/>
     </row>
-    <row r="175" ht="15" spans="2:5">
+    <row r="175" ht="15.75" spans="2:5">
       <c r="B175" s="11"/>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
       <c r="E175" s="2"/>
     </row>
-    <row r="176" ht="15" spans="2:5">
+    <row r="176" ht="15.75" spans="2:5">
       <c r="B176" s="11"/>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
       <c r="E176" s="2"/>
     </row>
-    <row r="177" ht="15" spans="2:5">
+    <row r="177" ht="15.75" spans="2:5">
       <c r="B177" s="11"/>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
       <c r="E177" s="2"/>
     </row>
-    <row r="178" ht="15" spans="2:5">
+    <row r="178" ht="15.75" spans="2:5">
       <c r="B178" s="11"/>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
       <c r="E178" s="2"/>
     </row>
-    <row r="179" ht="15" spans="2:5">
+    <row r="179" ht="15.75" spans="2:5">
       <c r="B179" s="11"/>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
       <c r="E179" s="2"/>
     </row>
-    <row r="180" ht="15" spans="2:5">
+    <row r="180" ht="15.75" spans="2:5">
       <c r="B180" s="11"/>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
       <c r="E180" s="2"/>
     </row>
-    <row r="181" ht="15" spans="2:5">
+    <row r="181" ht="15.75" spans="2:5">
       <c r="B181" s="11"/>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
       <c r="E181" s="2"/>
     </row>
-    <row r="182" ht="15" spans="2:5">
+    <row r="182" ht="15.75" spans="2:5">
       <c r="B182" s="11"/>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
       <c r="E182" s="2"/>
     </row>
-    <row r="183" ht="15" spans="2:5">
+    <row r="183" ht="15.75" spans="2:5">
       <c r="B183" s="11"/>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
       <c r="E183" s="2"/>
     </row>
-    <row r="184" ht="15" spans="2:5">
+    <row r="184" ht="15.75" spans="2:5">
       <c r="B184" s="11"/>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
       <c r="E184" s="2"/>
     </row>
-    <row r="185" ht="15" spans="2:5">
+    <row r="185" ht="15.75" spans="2:5">
       <c r="B185" s="11"/>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
       <c r="E185" s="2"/>
     </row>
-    <row r="186" ht="15" spans="2:5">
+    <row r="186" ht="15.75" spans="2:5">
       <c r="B186" s="11"/>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
       <c r="E186" s="2"/>
     </row>
-    <row r="187" ht="15" spans="2:5">
+    <row r="187" ht="15.75" spans="2:5">
       <c r="B187" s="11"/>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
       <c r="E187" s="2"/>
     </row>
-    <row r="188" ht="15" spans="2:5">
+    <row r="188" ht="15.75" spans="2:5">
       <c r="B188" s="11"/>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
       <c r="E188" s="2"/>
     </row>
-    <row r="189" ht="15" spans="2:5">
+    <row r="189" ht="15.75" spans="2:5">
       <c r="B189" s="11"/>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
       <c r="E189" s="2"/>
     </row>
-    <row r="190" ht="15" spans="2:5">
+    <row r="190" ht="15.75" spans="2:5">
       <c r="B190" s="11"/>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
       <c r="E190" s="2"/>
     </row>
-    <row r="191" ht="15" spans="2:5">
+    <row r="191" ht="15.75" spans="2:5">
       <c r="B191" s="11"/>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
       <c r="E191" s="2"/>
     </row>
-    <row r="192" ht="15" spans="2:5">
+    <row r="192" ht="15.75" spans="2:5">
       <c r="B192" s="11"/>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
       <c r="E192" s="2"/>
     </row>
-    <row r="193" ht="15" spans="2:5">
+    <row r="193" ht="15.75" spans="2:5">
       <c r="B193" s="11"/>
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
       <c r="E193" s="2"/>
     </row>
-    <row r="194" ht="15" spans="2:5">
+    <row r="194" ht="15.75" spans="2:5">
       <c r="B194" s="11"/>
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
       <c r="E194" s="2"/>
     </row>
-    <row r="195" ht="15" spans="2:5">
+    <row r="195" ht="15.75" spans="2:5">
       <c r="B195" s="11"/>
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
       <c r="E195" s="2"/>
     </row>
-    <row r="196" ht="15" spans="2:5">
+    <row r="196" ht="15.75" spans="2:5">
       <c r="B196" s="11"/>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
       <c r="E196" s="2"/>
     </row>
-    <row r="197" ht="15" spans="2:5">
+    <row r="197" ht="15.75" spans="2:5">
       <c r="B197" s="11"/>
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
       <c r="E197" s="2"/>
     </row>
-    <row r="198" ht="15" spans="2:5">
+    <row r="198" ht="15.75" spans="2:5">
       <c r="B198" s="11"/>
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
       <c r="E198" s="2"/>
     </row>
-    <row r="199" ht="15" spans="2:5">
+    <row r="199" ht="15.75" spans="2:5">
       <c r="B199" s="11"/>
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
       <c r="E199" s="2"/>
     </row>
-    <row r="200" ht="15" spans="2:5">
+    <row r="200" ht="15.75" spans="2:5">
       <c r="B200" s="11"/>
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
       <c r="E200" s="2"/>
     </row>
-    <row r="201" ht="15" spans="2:5">
+    <row r="201" ht="15.75" spans="2:5">
       <c r="B201" s="11"/>
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
       <c r="E201" s="2"/>
     </row>
-    <row r="202" ht="15" spans="2:5">
+    <row r="202" ht="15.75" spans="2:5">
       <c r="B202" s="11"/>
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
       <c r="E202" s="2"/>
     </row>
-    <row r="203" ht="15" spans="2:5">
+    <row r="203" ht="15.75" spans="2:5">
       <c r="B203" s="11"/>
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
       <c r="E203" s="2"/>
     </row>
-    <row r="204" ht="15" spans="2:5">
+    <row r="204" ht="15.75" spans="2:5">
       <c r="B204" s="11"/>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
       <c r="E204" s="2"/>
     </row>
-    <row r="205" ht="15" spans="2:5">
+    <row r="205" ht="15.75" spans="2:5">
       <c r="B205" s="11"/>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
       <c r="E205" s="2"/>
     </row>
-    <row r="206" ht="15" spans="2:5">
+    <row r="206" ht="15.75" spans="2:5">
       <c r="B206" s="11"/>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
       <c r="E206" s="2"/>
     </row>
-    <row r="207" ht="15" spans="2:5">
+    <row r="207" ht="15.75" spans="2:5">
       <c r="B207" s="11"/>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
       <c r="E207" s="2"/>
     </row>
-    <row r="208" ht="15" spans="2:5">
+    <row r="208" ht="15.75" spans="2:5">
       <c r="B208" s="11"/>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
       <c r="E208" s="2"/>
     </row>
-    <row r="209" ht="15" spans="2:5">
+    <row r="209" ht="15.75" spans="2:5">
       <c r="B209" s="11"/>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
       <c r="E209" s="2"/>
     </row>
-    <row r="210" ht="15" spans="2:5">
+    <row r="210" ht="15.75" spans="2:5">
       <c r="B210" s="11"/>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
       <c r="E210" s="2"/>
     </row>
-    <row r="211" ht="15" spans="2:5">
+    <row r="211" ht="15.75" spans="2:5">
       <c r="B211" s="11"/>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
       <c r="E211" s="2"/>
     </row>
-    <row r="212" ht="15" spans="2:5">
+    <row r="212" ht="15.75" spans="2:5">
       <c r="B212" s="11"/>
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
       <c r="E212" s="2"/>
     </row>
-    <row r="213" ht="15" spans="2:5">
+    <row r="213" ht="15.75" spans="2:5">
       <c r="B213" s="11"/>
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
       <c r="E213" s="2"/>
     </row>
-    <row r="214" ht="15" spans="2:5">
+    <row r="214" ht="15.75" spans="2:5">
       <c r="B214" s="11"/>
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
       <c r="E214" s="2"/>
     </row>
-    <row r="215" ht="15" spans="2:5">
+    <row r="215" ht="15.75" spans="2:5">
       <c r="B215" s="11"/>
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
       <c r="E215" s="2"/>
     </row>
-    <row r="216" ht="15" spans="2:5">
+    <row r="216" ht="15.75" spans="2:5">
       <c r="B216" s="11"/>
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
       <c r="E216" s="2"/>
     </row>
-    <row r="217" ht="15" spans="2:5">
+    <row r="217" ht="15.75" spans="2:5">
       <c r="B217" s="11"/>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
       <c r="E217" s="2"/>
     </row>
-    <row r="218" ht="15" spans="2:5">
+    <row r="218" ht="15.75" spans="2:5">
       <c r="B218" s="11"/>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
       <c r="E218" s="2"/>
     </row>
-    <row r="219" ht="15" spans="2:5">
+    <row r="219" ht="15.75" spans="2:5">
       <c r="B219" s="11"/>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
       <c r="E219" s="2"/>
     </row>
-    <row r="220" ht="15" spans="2:5">
+    <row r="220" ht="15.75" spans="2:5">
       <c r="B220" s="11"/>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
       <c r="E220" s="2"/>
     </row>
-    <row r="221" ht="15" spans="2:5">
+    <row r="221" ht="15.75" spans="2:5">
       <c r="B221" s="11"/>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
       <c r="E221" s="2"/>
     </row>
-    <row r="222" ht="15" spans="2:5">
+    <row r="222" ht="15.75" spans="2:5">
       <c r="B222" s="11"/>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
       <c r="E222" s="2"/>
     </row>
-    <row r="223" ht="15" spans="2:5">
+    <row r="223" ht="15.75" spans="2:5">
       <c r="B223" s="11"/>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
       <c r="E223" s="2"/>
     </row>
-    <row r="224" ht="15" spans="2:5">
+    <row r="224" ht="15.75" spans="2:5">
       <c r="B224" s="11"/>
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
       <c r="E224" s="2"/>
     </row>
-    <row r="225" ht="15" spans="2:5">
+    <row r="225" ht="15.75" spans="2:5">
       <c r="B225" s="11"/>
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
       <c r="E225" s="2"/>
     </row>
-    <row r="226" ht="15" spans="2:5">
+    <row r="226" ht="15.75" spans="2:5">
       <c r="B226" s="11"/>
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
       <c r="E226" s="2"/>
     </row>
-    <row r="227" ht="15" spans="2:5">
+    <row r="227" ht="15.75" spans="2:5">
       <c r="B227" s="11"/>
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
       <c r="E227" s="2"/>
     </row>
-    <row r="228" ht="15" spans="2:5">
+    <row r="228" ht="15.75" spans="2:5">
       <c r="B228" s="11"/>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
       <c r="E228" s="2"/>
     </row>
-    <row r="229" ht="15" spans="2:5">
+    <row r="229" ht="15.75" spans="2:5">
       <c r="B229" s="11"/>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
       <c r="E229" s="2"/>
     </row>
-    <row r="230" ht="15" spans="2:5">
+    <row r="230" ht="15.75" spans="2:5">
       <c r="B230" s="11"/>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
       <c r="E230" s="2"/>
     </row>
-    <row r="231" ht="15" spans="2:5">
+    <row r="231" ht="15.75" spans="2:5">
       <c r="B231" s="11"/>
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
       <c r="E231" s="2"/>
     </row>
-    <row r="232" ht="15" spans="2:5">
+    <row r="232" ht="15.75" spans="2:5">
       <c r="B232" s="11"/>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
       <c r="E232" s="2"/>
     </row>
-    <row r="233" ht="15" spans="2:5">
+    <row r="233" ht="15.75" spans="2:5">
       <c r="B233" s="11"/>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
       <c r="E233" s="2"/>
     </row>
-    <row r="234" ht="15" spans="2:5">
+    <row r="234" ht="15.75" spans="2:5">
       <c r="B234" s="11"/>
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
       <c r="E234" s="2"/>
     </row>
-    <row r="235" ht="15" spans="2:5">
+    <row r="235" ht="15.75" spans="2:5">
       <c r="B235" s="11"/>
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
       <c r="E235" s="2"/>
     </row>
-    <row r="236" ht="15" spans="2:5">
+    <row r="236" ht="15.75" spans="2:5">
       <c r="B236" s="11"/>
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
       <c r="E236" s="2"/>
     </row>
-    <row r="237" ht="15" spans="2:5">
+    <row r="237" ht="15.75" spans="2:5">
       <c r="B237" s="11"/>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
       <c r="E237" s="2"/>
     </row>
-    <row r="238" ht="15" spans="2:5">
+    <row r="238" ht="15.75" spans="2:5">
       <c r="B238" s="11"/>
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
       <c r="E238" s="2"/>
     </row>
-    <row r="239" ht="15" spans="2:5">
+    <row r="239" ht="15.75" spans="2:5">
       <c r="B239" s="11"/>
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
       <c r="E239" s="2"/>
     </row>
-    <row r="240" ht="15" spans="2:5">
+    <row r="240" ht="15.75" spans="2:5">
       <c r="B240" s="11"/>
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
       <c r="E240" s="2"/>
     </row>
-    <row r="241" ht="15" spans="2:5">
+    <row r="241" ht="15.75" spans="2:5">
       <c r="B241" s="11"/>
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
       <c r="E241" s="2"/>
     </row>
-    <row r="242" ht="15" spans="2:5">
+    <row r="242" ht="15.75" spans="2:5">
       <c r="B242" s="11"/>
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
       <c r="E242" s="2"/>
     </row>
-    <row r="243" ht="15" spans="2:5">
+    <row r="243" ht="15.75" spans="2:5">
       <c r="B243" s="11"/>
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
       <c r="E243" s="2"/>
     </row>
-    <row r="244" ht="15" spans="2:5">
+    <row r="244" ht="15.75" spans="2:5">
       <c r="B244" s="11"/>
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
       <c r="E244" s="2"/>
     </row>
-    <row r="245" ht="15" spans="2:5">
+    <row r="245" ht="15.75" spans="2:5">
       <c r="B245" s="11"/>
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
       <c r="E245" s="2"/>
     </row>
-    <row r="246" ht="15" spans="2:5">
+    <row r="246" ht="15.75" spans="2:5">
       <c r="B246" s="11"/>
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
       <c r="E246" s="2"/>
     </row>
-    <row r="247" ht="15" spans="2:5">
+    <row r="247" ht="15.75" spans="2:5">
       <c r="B247" s="11"/>
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
       <c r="E247" s="2"/>
     </row>
-    <row r="248" ht="15" spans="2:5">
+    <row r="248" ht="15.75" spans="2:5">
       <c r="B248" s="11"/>
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
       <c r="E248" s="2"/>
     </row>
-    <row r="249" ht="15" spans="2:5">
+    <row r="249" ht="15.75" spans="2:5">
       <c r="B249" s="11"/>
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
       <c r="E249" s="2"/>
     </row>
-    <row r="250" ht="15" spans="2:5">
+    <row r="250" ht="15.75" spans="2:5">
       <c r="B250" s="11"/>
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
       <c r="E250" s="2"/>
     </row>
-    <row r="251" ht="15" spans="2:5">
+    <row r="251" ht="15.75" spans="2:5">
       <c r="B251" s="11"/>
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
       <c r="E251" s="2"/>
     </row>
-    <row r="252" ht="15" spans="2:5">
+    <row r="252" ht="15.75" spans="2:5">
       <c r="B252" s="11"/>
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
       <c r="E252" s="2"/>
     </row>
-    <row r="253" ht="15" spans="2:5">
+    <row r="253" ht="15.75" spans="2:5">
       <c r="B253" s="11"/>
       <c r="C253" s="7"/>
       <c r="D253" s="7"/>
       <c r="E253" s="2"/>
     </row>
-    <row r="254" ht="15" spans="2:5">
+    <row r="254" ht="15.75" spans="2:5">
       <c r="B254" s="11"/>
       <c r="C254" s="7"/>
       <c r="D254" s="7"/>
       <c r="E254" s="2"/>
     </row>
-    <row r="255" ht="15" spans="2:5">
+    <row r="255" ht="15.75" spans="2:5">
       <c r="B255" s="11"/>
       <c r="C255" s="7"/>
       <c r="D255" s="7"/>
       <c r="E255" s="2"/>
     </row>
-    <row r="256" ht="15" spans="2:5">
+    <row r="256" ht="15.75" spans="2:5">
       <c r="B256" s="11"/>
       <c r="C256" s="7"/>
       <c r="D256" s="7"/>
       <c r="E256" s="2"/>
     </row>
-    <row r="257" ht="15" spans="2:5">
+    <row r="257" ht="15.75" spans="2:5">
       <c r="B257" s="11"/>
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
       <c r="E257" s="2"/>
     </row>
-    <row r="258" ht="15" spans="2:5">
+    <row r="258" ht="15.75" spans="2:5">
       <c r="B258" s="11"/>
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
       <c r="E258" s="2"/>
     </row>
-    <row r="259" ht="15" spans="2:5">
+    <row r="259" ht="15.75" spans="2:5">
       <c r="B259" s="11"/>
       <c r="C259" s="7"/>
       <c r="D259" s="7"/>
       <c r="E259" s="2"/>
     </row>
-    <row r="260" ht="15" spans="2:5">
+    <row r="260" ht="15.75" spans="2:5">
       <c r="B260" s="11"/>
       <c r="C260" s="7"/>
       <c r="D260" s="7"/>
       <c r="E260" s="2"/>
     </row>
-    <row r="261" ht="15" spans="2:5">
+    <row r="261" ht="15.75" spans="2:5">
       <c r="B261" s="11"/>
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
       <c r="E261" s="2"/>
     </row>
-    <row r="262" ht="15" spans="2:5">
+    <row r="262" ht="15.75" spans="2:5">
       <c r="B262" s="11"/>
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
       <c r="E262" s="2"/>
     </row>
-    <row r="263" ht="15" spans="2:5">
+    <row r="263" ht="15.75" spans="2:5">
       <c r="B263" s="11"/>
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
       <c r="E263" s="2"/>
     </row>
-    <row r="264" ht="15" spans="2:5">
+    <row r="264" ht="15.75" spans="2:5">
       <c r="B264" s="11"/>
       <c r="C264" s="7"/>
       <c r="D264" s="7"/>
       <c r="E264" s="2"/>
     </row>
-    <row r="265" ht="15" spans="2:5">
+    <row r="265" ht="15.75" spans="2:5">
       <c r="B265" s="11"/>
       <c r="C265" s="7"/>
       <c r="D265" s="7"/>
       <c r="E265" s="2"/>
     </row>
-    <row r="266" ht="15" spans="2:5">
+    <row r="266" ht="15.75" spans="2:5">
       <c r="B266" s="11"/>
       <c r="C266" s="7"/>
       <c r="D266" s="7"/>
       <c r="E266" s="2"/>
     </row>
-    <row r="267" ht="15" spans="2:5">
+    <row r="267" ht="15.75" spans="2:5">
       <c r="B267" s="11"/>
       <c r="C267" s="7"/>
       <c r="D267" s="7"/>
       <c r="E267" s="2"/>
     </row>
-    <row r="268" ht="15" spans="2:5">
+    <row r="268" ht="15.75" spans="2:5">
       <c r="B268" s="11"/>
       <c r="C268" s="7"/>
       <c r="D268" s="7"/>
       <c r="E268" s="2"/>
     </row>
-    <row r="269" ht="15" spans="2:5">
+    <row r="269" ht="15.75" spans="2:5">
       <c r="B269" s="11"/>
       <c r="C269" s="7"/>
       <c r="D269" s="7"/>
       <c r="E269" s="2"/>
     </row>
-    <row r="270" ht="15" spans="2:5">
+    <row r="270" ht="15.75" spans="2:5">
       <c r="B270" s="11"/>
       <c r="C270" s="7"/>
       <c r="D270" s="7"/>
       <c r="E270" s="2"/>
     </row>
-    <row r="271" ht="15" spans="2:5">
+    <row r="271" ht="15.75" spans="2:5">
       <c r="B271" s="11"/>
       <c r="C271" s="7"/>
       <c r="D271" s="7"/>
       <c r="E271" s="2"/>
     </row>
-    <row r="272" ht="15" spans="2:5">
+    <row r="272" ht="15.75" spans="2:5">
       <c r="B272" s="11"/>
       <c r="C272" s="7"/>
       <c r="D272" s="7"/>
       <c r="E272" s="2"/>
     </row>
-    <row r="273" ht="15" spans="2:5">
+    <row r="273" ht="15.75" spans="2:5">
       <c r="B273" s="11"/>
       <c r="C273" s="7"/>
       <c r="D273" s="7"/>
       <c r="E273" s="2"/>
     </row>
-    <row r="274" ht="15" spans="2:5">
+    <row r="274" ht="15.75" spans="2:5">
       <c r="B274" s="11"/>
       <c r="C274" s="7"/>
       <c r="D274" s="7"/>
       <c r="E274" s="2"/>
     </row>
-    <row r="275" ht="15" spans="2:5">
+    <row r="275" ht="15.75" spans="2:5">
       <c r="B275" s="11"/>
       <c r="C275" s="7"/>
       <c r="D275" s="7"/>
       <c r="E275" s="2"/>
     </row>
-    <row r="276" ht="15" spans="2:5">
+    <row r="276" ht="15.75" spans="2:5">
       <c r="B276" s="11"/>
       <c r="C276" s="7"/>
       <c r="D276" s="7"/>
       <c r="E276" s="2"/>
     </row>
-    <row r="277" ht="15" spans="2:5">
+    <row r="277" ht="15.75" spans="2:5">
       <c r="B277" s="11"/>
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
       <c r="E277" s="2"/>
     </row>
-    <row r="278" ht="15" spans="2:5">
+    <row r="278" ht="15.75" spans="2:5">
       <c r="B278" s="11"/>
       <c r="C278" s="7"/>
       <c r="D278" s="7"/>
       <c r="E278" s="2"/>
     </row>
-    <row r="279" ht="15" spans="2:5">
+    <row r="279" ht="15.75" spans="2:5">
       <c r="B279" s="11"/>
       <c r="C279" s="7"/>
       <c r="D279" s="7"/>
       <c r="E279" s="2"/>
     </row>
-    <row r="280" ht="15" spans="2:5">
+    <row r="280" ht="15.75" spans="2:5">
       <c r="B280" s="11"/>
       <c r="C280" s="7"/>
       <c r="D280" s="7"/>
       <c r="E280" s="2"/>
     </row>
-    <row r="281" ht="15" spans="2:5">
+    <row r="281" ht="15.75" spans="2:5">
       <c r="B281" s="11"/>
       <c r="C281" s="7"/>
       <c r="D281" s="7"/>
       <c r="E281" s="2"/>
     </row>
-    <row r="282" ht="15" spans="2:5">
+    <row r="282" ht="15.75" spans="2:5">
       <c r="B282" s="11"/>
       <c r="C282" s="7"/>
       <c r="D282" s="7"/>
       <c r="E282" s="2"/>
     </row>
-    <row r="283" ht="15" spans="2:5">
+    <row r="283" ht="15.75" spans="2:5">
       <c r="B283" s="11"/>
       <c r="C283" s="7"/>
       <c r="D283" s="7"/>
       <c r="E283" s="2"/>
     </row>
-    <row r="284" ht="15" spans="2:5">
+    <row r="284" ht="15.75" spans="2:5">
       <c r="B284" s="11"/>
       <c r="C284" s="7"/>
       <c r="D284" s="7"/>
       <c r="E284" s="2"/>
     </row>
-    <row r="285" ht="15" spans="2:5">
+    <row r="285" ht="15.75" spans="2:5">
       <c r="B285" s="11"/>
       <c r="C285" s="7"/>
       <c r="D285" s="7"/>
       <c r="E285" s="2"/>
     </row>
-    <row r="286" ht="15" spans="2:5">
+    <row r="286" ht="15.75" spans="2:5">
       <c r="B286" s="11"/>
       <c r="C286" s="7"/>
       <c r="D286" s="7"/>
       <c r="E286" s="2"/>
     </row>
-    <row r="287" ht="15" spans="2:5">
+    <row r="287" ht="15.75" spans="2:5">
       <c r="B287" s="11"/>
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
       <c r="E287" s="2"/>
     </row>
-    <row r="288" ht="15" spans="2:5">
+    <row r="288" ht="15.75" spans="2:5">
       <c r="B288" s="11"/>
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
       <c r="E288" s="2"/>
     </row>
-    <row r="289" ht="15" spans="2:5">
+    <row r="289" ht="15.75" spans="2:5">
       <c r="B289" s="11"/>
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
       <c r="E289" s="2"/>
     </row>
-    <row r="290" ht="15" spans="2:5">
+    <row r="290" ht="15.75" spans="2:5">
       <c r="B290" s="11"/>
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
       <c r="E290" s="2"/>
     </row>
-    <row r="291" ht="15" spans="2:5">
+    <row r="291" ht="15.75" spans="2:5">
       <c r="B291" s="11"/>
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
       <c r="E291" s="2"/>
     </row>
-    <row r="292" ht="15" spans="2:5">
+    <row r="292" ht="15.75" spans="2:5">
       <c r="B292" s="11"/>
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
       <c r="E292" s="2"/>
     </row>
-    <row r="293" ht="14.25"/>
+    <row r="293" ht="15"/>
   </sheetData>
   <conditionalFormatting sqref="C3:C292">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -3145,7 +3163,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="30.2166666666667" customWidth="1"/>
     <col min="2" max="2" width="14.5583333333333" style="1" customWidth="1"/>
@@ -3154,26 +3172,26 @@
     <col min="7" max="18" width="14.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:18">
+    <row r="1" ht="15.75" spans="1:18">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="4"/>
       <c r="F1" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="5"/>
       <c r="I1" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J1" s="2"/>
       <c r="K1" s="6"/>
       <c r="L1" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
@@ -3182,7 +3200,7 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
     </row>
-    <row r="2" ht="15" spans="1:18">
+    <row r="2" ht="15.75" spans="1:18">
       <c r="A2" s="2"/>
       <c r="B2" s="7"/>
       <c r="C2" s="2"/>
@@ -3202,61 +3220,61 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" ht="15" spans="1:18">
+    <row r="3" ht="15.75" spans="1:18">
       <c r="A3" s="2"/>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="L3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="M3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="N3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="Q3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="R3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" ht="15" spans="1:18">
+    </row>
+    <row r="4" ht="15.75" spans="1:18">
       <c r="A4" s="2"/>
       <c r="B4" s="9">
         <v>46281</v>
@@ -3310,9 +3328,9 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="1:18">
+    <row r="5" ht="15.75" spans="1:18">
       <c r="A5" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>5</v>
@@ -3334,9 +3352,9 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" ht="15" spans="1:18">
+    <row r="6" ht="15.75" spans="1:18">
       <c r="A6" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>5</v>
@@ -3358,9 +3376,9 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" ht="15" spans="1:18">
+    <row r="7" ht="15.75" spans="1:18">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>5</v>
@@ -3382,9 +3400,9 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" ht="15" spans="1:18">
+    <row r="8" ht="15.75" spans="1:18">
       <c r="A8" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>12</v>
@@ -3408,9 +3426,9 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
     </row>
-    <row r="9" ht="15" spans="1:18">
+    <row r="9" ht="15.75" spans="1:18">
       <c r="A9" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>5</v>
@@ -3432,9 +3450,9 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" ht="15" spans="1:18">
+    <row r="10" ht="15.75" spans="1:18">
       <c r="A10" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>12</v>
@@ -3458,9 +3476,9 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" ht="15" spans="1:18">
+    <row r="11" ht="15.75" spans="1:18">
       <c r="A11" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>5</v>
@@ -3482,9 +3500,9 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" ht="15" spans="1:18">
+    <row r="12" ht="15.75" spans="1:18">
       <c r="A12" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>12</v>
@@ -3508,9 +3526,9 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" ht="15" spans="1:18">
+    <row r="13" ht="15.75" spans="1:18">
       <c r="A13" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>12</v>
@@ -3534,9 +3552,9 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" ht="15" spans="1:18">
+    <row r="14" ht="15.75" spans="1:18">
       <c r="A14" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>5</v>
@@ -3558,9 +3576,9 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" ht="15" spans="1:18">
+    <row r="15" ht="15.75" spans="1:18">
       <c r="A15" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="2" t="s">
@@ -3582,9 +3600,9 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" ht="15" spans="1:18">
+    <row r="16" ht="15.75" spans="1:18">
       <c r="A16" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="2" t="s">
@@ -3606,9 +3624,9 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" ht="15" spans="1:18">
+    <row r="17" ht="15.75" spans="1:18">
       <c r="A17" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="2" t="s">
@@ -3634,9 +3652,9 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" ht="15" spans="1:18">
+    <row r="18" ht="15.75" spans="1:18">
       <c r="A18" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="2" t="s">
@@ -3662,13 +3680,13 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" ht="15" spans="1:18">
+    <row r="19" ht="15.75" spans="1:18">
       <c r="A19" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -3690,13 +3708,13 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" ht="15" spans="1:18">
+    <row r="20" ht="15.75" spans="1:18">
       <c r="A20" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -3718,16 +3736,16 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" ht="15" spans="1:18">
+    <row r="21" ht="15.75" spans="1:18">
       <c r="A21" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -3746,16 +3764,16 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" ht="15" spans="1:18">
+    <row r="22" ht="15.75" spans="1:18">
       <c r="A22" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
@@ -3774,16 +3792,16 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" ht="15" spans="1:18">
+    <row r="23" ht="15.75" spans="1:18">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
@@ -3802,16 +3820,16 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" ht="15" spans="1:18">
+    <row r="24" ht="15.75" spans="1:18">
       <c r="A24" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -3832,9 +3850,9 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" ht="15" spans="1:18">
+    <row r="25" ht="15.75" spans="1:18">
       <c r="A25" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="2"/>
@@ -3858,9 +3876,9 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" ht="15" spans="1:18">
+    <row r="26" ht="15.75" spans="1:18">
       <c r="A26" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="2"/>
@@ -3884,9 +3902,9 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" ht="15" spans="1:18">
+    <row r="27" ht="15.75" spans="1:18">
       <c r="A27" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="2"/>
@@ -3910,9 +3928,9 @@
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" ht="15" spans="1:18">
+    <row r="28" ht="15.75" spans="1:18">
       <c r="A28" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="2"/>
@@ -3936,7 +3954,7 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" ht="14.25"/>
+    <row r="29" ht="15"/>
   </sheetData>
   <conditionalFormatting sqref="B5:R28">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">

--- a/Documentos/Outros/BES3543 - Status Comissionamento.xlsx
+++ b/Documentos/Outros/BES3543 - Status Comissionamento.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11580"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Pendencias " sheetId="2" r:id="rId1"/>
@@ -54,31 +54,31 @@
     <t>Melhoria na rotina de Pesagem</t>
   </si>
   <si>
+    <t>Teste Troca de Sinais Máquina Valgroup</t>
+  </si>
+  <si>
+    <t>Lógica Posicionador</t>
+  </si>
+  <si>
+    <t>Inserir botão Máquina Acoplada na IHM</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>28/set</t>
+  </si>
+  <si>
+    <t>Validação de Tela de Contagem e Dados</t>
+  </si>
+  <si>
+    <t>30/set</t>
+  </si>
+  <si>
+    <t>Separação de Botões de Comando Porta e Botoeira Central</t>
+  </si>
+  <si>
     <t>ip</t>
-  </si>
-  <si>
-    <t>Teste Troca de Sinais Máquina Valgroup</t>
-  </si>
-  <si>
-    <t>Lógica Posicionador</t>
-  </si>
-  <si>
-    <t>Inserir botão Máquina Acoplada na IHM</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>28/set</t>
-  </si>
-  <si>
-    <t>Validação de Tela de Contagem e Dados</t>
-  </si>
-  <si>
-    <t>30/set</t>
-  </si>
-  <si>
-    <t>Separação de Botões de Comando Porta e Botoeira Central</t>
   </si>
   <si>
     <t>Teste de ciclo real para função de Inspeção</t>
@@ -373,7 +373,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -419,6 +419,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -754,7 +760,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -778,16 +784,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -796,89 +802,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -920,6 +926,9 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1294,7 +1303,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:E293"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="82.4416666666667" style="15" customWidth="1"/>
@@ -1303,8 +1312,8 @@
     <col min="5" max="5" width="62.2166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15"/>
-    <row r="2" ht="16.5" spans="2:5">
+    <row r="1" ht="14.55"/>
+    <row r="2" ht="15.3" spans="2:5">
       <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
@@ -1318,7 +1327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="15.75" spans="2:5">
+    <row r="3" ht="15.3" spans="2:5">
       <c r="B3" s="11" t="s">
         <v>4</v>
       </c>
@@ -1330,7 +1339,7 @@
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" ht="15.75" spans="2:5">
+    <row r="4" ht="15.3" spans="2:5">
       <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
@@ -1342,19 +1351,19 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" ht="15.75" spans="2:5">
+    <row r="5" ht="15.3" spans="2:5">
       <c r="B5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>8</v>
+      <c r="C5" s="17" t="s">
+        <v>5</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" ht="15.75" spans="2:5">
+    <row r="6" ht="15.3" spans="2:5">
       <c r="B6" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>5</v>
@@ -1364,9 +1373,9 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" ht="15.75" spans="2:5">
+    <row r="7" ht="15.3" spans="2:5">
       <c r="B7" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>5</v>
@@ -1376,41 +1385,41 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" ht="15.75" spans="2:5">
+    <row r="8" ht="15.3" spans="2:5">
       <c r="B8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" ht="15.3" spans="2:5">
+      <c r="B9" s="11" t="s">
         <v>13</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" ht="15.75" spans="2:5">
-      <c r="B9" s="11" t="s">
-        <v>14</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" ht="15.3" spans="2:5">
+      <c r="B10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" ht="15.75" spans="2:5">
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" ht="15.75" spans="2:5">
+    <row r="11" ht="15.3" spans="2:5">
       <c r="B11" s="11" t="s">
         <v>17</v>
       </c>
@@ -1422,43 +1431,43 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" ht="15.75" spans="2:5">
+    <row r="12" ht="15.3" spans="2:5">
       <c r="B12" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" ht="15.75" spans="2:5">
+    <row r="13" ht="15.3" spans="2:5">
       <c r="B13" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" ht="15.75" spans="2:5">
+    <row r="14" ht="15.3" spans="2:5">
       <c r="B14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" ht="15.75" spans="2:5">
+    <row r="15" ht="15.3" spans="2:5">
       <c r="B15" s="11" t="s">
         <v>21</v>
       </c>
@@ -1468,7 +1477,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" ht="15.75" spans="2:5">
+    <row r="16" ht="15.3" spans="2:5">
       <c r="B16" s="11" t="s">
         <v>23</v>
       </c>
@@ -1476,1671 +1485,1671 @@
         <v>5</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" ht="15.75" spans="2:5">
+    <row r="17" ht="15.3" spans="2:5">
       <c r="B17" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" ht="15.75" spans="2:5">
+    <row r="18" ht="15.3" spans="2:5">
       <c r="B18" s="11"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" ht="15.75" spans="2:5">
+    <row r="19" ht="15.3" spans="2:5">
       <c r="B19" s="11"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" ht="15.75" spans="2:5">
+    <row r="20" ht="15.3" spans="2:5">
       <c r="B20" s="11"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" ht="15.75" spans="2:5">
+    <row r="21" ht="15.3" spans="2:5">
       <c r="B21" s="11"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" ht="15.75" spans="2:5">
+    <row r="22" ht="15.3" spans="2:5">
       <c r="B22" s="11"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" ht="15.75" spans="2:5">
+    <row r="23" ht="15.3" spans="2:5">
       <c r="B23" s="11"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" ht="15.75" spans="2:5">
+    <row r="24" ht="15.3" spans="2:5">
       <c r="B24" s="11"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" ht="15.75" spans="2:5">
+    <row r="25" ht="15.3" spans="2:5">
       <c r="B25" s="11"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" ht="15.75" spans="2:5">
+    <row r="26" ht="15.3" spans="2:5">
       <c r="B26" s="11"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" ht="15.75" spans="2:5">
+    <row r="27" ht="15.3" spans="2:5">
       <c r="B27" s="11"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" ht="15.75" spans="2:5">
+    <row r="28" ht="15.3" spans="2:5">
       <c r="B28" s="11"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" ht="15.75" spans="2:5">
+    <row r="29" ht="15.3" spans="2:5">
       <c r="B29" s="11"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" ht="15.75" spans="2:5">
+    <row r="30" ht="15.3" spans="2:5">
       <c r="B30" s="11"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" ht="15.75" spans="2:5">
+    <row r="31" ht="15.3" spans="2:5">
       <c r="B31" s="11"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" ht="15.75" spans="2:5">
+    <row r="32" ht="15.3" spans="2:5">
       <c r="B32" s="11"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" ht="15.75" spans="2:5">
+    <row r="33" ht="15.3" spans="2:5">
       <c r="B33" s="11"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" ht="15.75" spans="2:5">
+    <row r="34" ht="15.3" spans="2:5">
       <c r="B34" s="11"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" ht="15.75" spans="2:5">
+    <row r="35" ht="15.3" spans="2:5">
       <c r="B35" s="11"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" ht="15.75" spans="2:5">
+    <row r="36" ht="15.3" spans="2:5">
       <c r="B36" s="11"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" ht="15.75" spans="2:5">
+    <row r="37" ht="15.3" spans="2:5">
       <c r="B37" s="11"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" ht="15.75" spans="2:5">
+    <row r="38" ht="15.3" spans="2:5">
       <c r="B38" s="11"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" ht="15.75" spans="2:5">
+    <row r="39" ht="15.3" spans="2:5">
       <c r="B39" s="11"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="2"/>
     </row>
-    <row r="40" ht="15.75" spans="2:5">
+    <row r="40" ht="15.3" spans="2:5">
       <c r="B40" s="11"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" ht="15.75" spans="2:5">
+    <row r="41" ht="15.3" spans="2:5">
       <c r="B41" s="11"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" ht="15.75" spans="2:5">
+    <row r="42" ht="15.3" spans="2:5">
       <c r="B42" s="11"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" ht="15.75" spans="2:5">
+    <row r="43" ht="15.3" spans="2:5">
       <c r="B43" s="11"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" ht="15.75" spans="2:5">
+    <row r="44" ht="15.3" spans="2:5">
       <c r="B44" s="11"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" ht="15.75" spans="2:5">
+    <row r="45" ht="15.3" spans="2:5">
       <c r="B45" s="11"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" ht="15.75" spans="2:5">
+    <row r="46" ht="15.3" spans="2:5">
       <c r="B46" s="11"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" ht="15.75" spans="2:5">
+    <row r="47" ht="15.3" spans="2:5">
       <c r="B47" s="11"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" ht="15.75" spans="2:5">
+    <row r="48" ht="15.3" spans="2:5">
       <c r="B48" s="11"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" ht="15.75" spans="2:5">
+    <row r="49" ht="15.3" spans="2:5">
       <c r="B49" s="11"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" ht="15.75" spans="2:5">
+    <row r="50" ht="15.3" spans="2:5">
       <c r="B50" s="11"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" ht="15.75" spans="2:5">
+    <row r="51" ht="15.3" spans="2:5">
       <c r="B51" s="11"/>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="2"/>
     </row>
-    <row r="52" ht="15.75" spans="2:5">
+    <row r="52" ht="15.3" spans="2:5">
       <c r="B52" s="11"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" ht="15.75" spans="2:5">
+    <row r="53" ht="15.3" spans="2:5">
       <c r="B53" s="11"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" ht="15.75" spans="2:5">
+    <row r="54" ht="15.3" spans="2:5">
       <c r="B54" s="11"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" ht="15.75" spans="2:5">
+    <row r="55" ht="15.3" spans="2:5">
       <c r="B55" s="11"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" ht="15.75" spans="2:5">
+    <row r="56" ht="15.3" spans="2:5">
       <c r="B56" s="11"/>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" ht="15.75" spans="2:5">
+    <row r="57" ht="15.3" spans="2:5">
       <c r="B57" s="11"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" ht="15.75" spans="2:5">
+    <row r="58" ht="15.3" spans="2:5">
       <c r="B58" s="11"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" ht="15.75" spans="2:5">
+    <row r="59" ht="15.3" spans="2:5">
       <c r="B59" s="11"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" ht="15.75" spans="2:5">
+    <row r="60" ht="15.3" spans="2:5">
       <c r="B60" s="11"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="2"/>
     </row>
-    <row r="61" ht="15.75" spans="2:5">
+    <row r="61" ht="15.3" spans="2:5">
       <c r="B61" s="11"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" ht="15.75" spans="2:5">
+    <row r="62" ht="15.3" spans="2:5">
       <c r="B62" s="11"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" ht="15.75" spans="2:5">
+    <row r="63" ht="15.3" spans="2:5">
       <c r="B63" s="11"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" ht="15.75" spans="2:5">
+    <row r="64" ht="15.3" spans="2:5">
       <c r="B64" s="11"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" ht="15.75" spans="2:5">
+    <row r="65" ht="15.3" spans="2:5">
       <c r="B65" s="11"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" ht="15.75" spans="2:5">
+    <row r="66" ht="15.3" spans="2:5">
       <c r="B66" s="11"/>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="2"/>
     </row>
-    <row r="67" ht="15.75" spans="2:5">
+    <row r="67" ht="15.3" spans="2:5">
       <c r="B67" s="11"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
       <c r="E67" s="2"/>
     </row>
-    <row r="68" ht="15.75" spans="2:5">
+    <row r="68" ht="15.3" spans="2:5">
       <c r="B68" s="11"/>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
       <c r="E68" s="2"/>
     </row>
-    <row r="69" ht="15.75" spans="2:5">
+    <row r="69" ht="15.3" spans="2:5">
       <c r="B69" s="11"/>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" ht="15.75" spans="2:5">
+    <row r="70" ht="15.3" spans="2:5">
       <c r="B70" s="11"/>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" ht="15.75" spans="2:5">
+    <row r="71" ht="15.3" spans="2:5">
       <c r="B71" s="11"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
       <c r="E71" s="2"/>
     </row>
-    <row r="72" ht="15.75" spans="2:5">
+    <row r="72" ht="15.3" spans="2:5">
       <c r="B72" s="11"/>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" ht="15.75" spans="2:5">
+    <row r="73" ht="15.3" spans="2:5">
       <c r="B73" s="11"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
       <c r="E73" s="2"/>
     </row>
-    <row r="74" ht="15.75" spans="2:5">
+    <row r="74" ht="15.3" spans="2:5">
       <c r="B74" s="11"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="E74" s="2"/>
     </row>
-    <row r="75" ht="15.75" spans="2:5">
+    <row r="75" ht="15.3" spans="2:5">
       <c r="B75" s="11"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" ht="15.75" spans="2:5">
+    <row r="76" ht="15.3" spans="2:5">
       <c r="B76" s="11"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" ht="15.75" spans="2:5">
+    <row r="77" ht="15.3" spans="2:5">
       <c r="B77" s="11"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" ht="15.75" spans="2:5">
+    <row r="78" ht="15.3" spans="2:5">
       <c r="B78" s="11"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" ht="15.75" spans="2:5">
+    <row r="79" ht="15.3" spans="2:5">
       <c r="B79" s="11"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" ht="15.75" spans="2:5">
+    <row r="80" ht="15.3" spans="2:5">
       <c r="B80" s="11"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" ht="15.75" spans="2:5">
+    <row r="81" ht="15.3" spans="2:5">
       <c r="B81" s="11"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" ht="15.75" spans="2:5">
+    <row r="82" ht="15.3" spans="2:5">
       <c r="B82" s="11"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" ht="15.75" spans="2:5">
+    <row r="83" ht="15.3" spans="2:5">
       <c r="B83" s="11"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" ht="15.75" spans="2:5">
+    <row r="84" ht="15.3" spans="2:5">
       <c r="B84" s="11"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" ht="15.75" spans="2:5">
+    <row r="85" ht="15.3" spans="2:5">
       <c r="B85" s="11"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="E85" s="2"/>
     </row>
-    <row r="86" ht="15.75" spans="2:5">
+    <row r="86" ht="15.3" spans="2:5">
       <c r="B86" s="11"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="2"/>
     </row>
-    <row r="87" ht="15.75" spans="2:5">
+    <row r="87" ht="15.3" spans="2:5">
       <c r="B87" s="11"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="2"/>
     </row>
-    <row r="88" ht="15.75" spans="2:5">
+    <row r="88" ht="15.3" spans="2:5">
       <c r="B88" s="11"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" ht="15.75" spans="2:5">
+    <row r="89" ht="15.3" spans="2:5">
       <c r="B89" s="11"/>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" ht="15.75" spans="2:5">
+    <row r="90" ht="15.3" spans="2:5">
       <c r="B90" s="11"/>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" ht="15.75" spans="2:5">
+    <row r="91" ht="15.3" spans="2:5">
       <c r="B91" s="11"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
       <c r="E91" s="2"/>
     </row>
-    <row r="92" ht="15.75" spans="2:5">
+    <row r="92" ht="15.3" spans="2:5">
       <c r="B92" s="11"/>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
       <c r="E92" s="2"/>
     </row>
-    <row r="93" ht="15.75" spans="2:5">
+    <row r="93" ht="15.3" spans="2:5">
       <c r="B93" s="11"/>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="2"/>
     </row>
-    <row r="94" ht="15.75" spans="2:5">
+    <row r="94" ht="15.3" spans="2:5">
       <c r="B94" s="11"/>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" ht="15.75" spans="2:5">
+    <row r="95" ht="15.3" spans="2:5">
       <c r="B95" s="11"/>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
       <c r="E95" s="2"/>
     </row>
-    <row r="96" ht="15.75" spans="2:5">
+    <row r="96" ht="15.3" spans="2:5">
       <c r="B96" s="11"/>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" ht="15.75" spans="2:5">
+    <row r="97" ht="15.3" spans="2:5">
       <c r="B97" s="11"/>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" ht="15.75" spans="2:5">
+    <row r="98" ht="15.3" spans="2:5">
       <c r="B98" s="11"/>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
       <c r="E98" s="2"/>
     </row>
-    <row r="99" ht="15.75" spans="2:5">
+    <row r="99" ht="15.3" spans="2:5">
       <c r="B99" s="11"/>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" ht="15.75" spans="2:5">
+    <row r="100" ht="15.3" spans="2:5">
       <c r="B100" s="11"/>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" ht="15.75" spans="2:5">
+    <row r="101" ht="15.3" spans="2:5">
       <c r="B101" s="11"/>
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
       <c r="E101" s="2"/>
     </row>
-    <row r="102" ht="15.75" spans="2:5">
+    <row r="102" ht="15.3" spans="2:5">
       <c r="B102" s="11"/>
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" ht="15.75" spans="2:5">
+    <row r="103" ht="15.3" spans="2:5">
       <c r="B103" s="11"/>
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" ht="15.75" spans="2:5">
+    <row r="104" ht="15.3" spans="2:5">
       <c r="B104" s="11"/>
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" ht="15.75" spans="2:5">
+    <row r="105" ht="15.3" spans="2:5">
       <c r="B105" s="11"/>
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" ht="15.75" spans="2:5">
+    <row r="106" ht="15.3" spans="2:5">
       <c r="B106" s="11"/>
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" ht="15.75" spans="2:5">
+    <row r="107" ht="15.3" spans="2:5">
       <c r="B107" s="11"/>
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
       <c r="E107" s="2"/>
     </row>
-    <row r="108" ht="15.75" spans="2:5">
+    <row r="108" ht="15.3" spans="2:5">
       <c r="B108" s="11"/>
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
       <c r="E108" s="2"/>
     </row>
-    <row r="109" ht="15.75" spans="2:5">
+    <row r="109" ht="15.3" spans="2:5">
       <c r="B109" s="11"/>
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
       <c r="E109" s="2"/>
     </row>
-    <row r="110" ht="15.75" spans="2:5">
+    <row r="110" ht="15.3" spans="2:5">
       <c r="B110" s="11"/>
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
       <c r="E110" s="2"/>
     </row>
-    <row r="111" ht="15.75" spans="2:5">
+    <row r="111" ht="15.3" spans="2:5">
       <c r="B111" s="11"/>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
       <c r="E111" s="2"/>
     </row>
-    <row r="112" ht="15.75" spans="2:5">
+    <row r="112" ht="15.3" spans="2:5">
       <c r="B112" s="11"/>
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
       <c r="E112" s="2"/>
     </row>
-    <row r="113" ht="15.75" spans="2:5">
+    <row r="113" ht="15.3" spans="2:5">
       <c r="B113" s="11"/>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
       <c r="E113" s="2"/>
     </row>
-    <row r="114" ht="15.75" spans="2:5">
+    <row r="114" ht="15.3" spans="2:5">
       <c r="B114" s="11"/>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
       <c r="E114" s="2"/>
     </row>
-    <row r="115" ht="15.75" spans="2:5">
+    <row r="115" ht="15.3" spans="2:5">
       <c r="B115" s="11"/>
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
       <c r="E115" s="2"/>
     </row>
-    <row r="116" ht="15.75" spans="2:5">
+    <row r="116" ht="15.3" spans="2:5">
       <c r="B116" s="11"/>
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
       <c r="E116" s="2"/>
     </row>
-    <row r="117" ht="15.75" spans="2:5">
+    <row r="117" ht="15.3" spans="2:5">
       <c r="B117" s="11"/>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
       <c r="E117" s="2"/>
     </row>
-    <row r="118" ht="15.75" spans="2:5">
+    <row r="118" ht="15.3" spans="2:5">
       <c r="B118" s="11"/>
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
       <c r="E118" s="2"/>
     </row>
-    <row r="119" ht="15.75" spans="2:5">
+    <row r="119" ht="15.3" spans="2:5">
       <c r="B119" s="11"/>
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
       <c r="E119" s="2"/>
     </row>
-    <row r="120" ht="15.75" spans="2:5">
+    <row r="120" ht="15.3" spans="2:5">
       <c r="B120" s="11"/>
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
       <c r="E120" s="2"/>
     </row>
-    <row r="121" ht="15.75" spans="2:5">
+    <row r="121" ht="15.3" spans="2:5">
       <c r="B121" s="11"/>
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
       <c r="E121" s="2"/>
     </row>
-    <row r="122" ht="15.75" spans="2:5">
+    <row r="122" ht="15.3" spans="2:5">
       <c r="B122" s="11"/>
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
       <c r="E122" s="2"/>
     </row>
-    <row r="123" ht="15.75" spans="2:5">
+    <row r="123" ht="15.3" spans="2:5">
       <c r="B123" s="11"/>
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
       <c r="E123" s="2"/>
     </row>
-    <row r="124" ht="15.75" spans="2:5">
+    <row r="124" ht="15.3" spans="2:5">
       <c r="B124" s="11"/>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
       <c r="E124" s="2"/>
     </row>
-    <row r="125" ht="15.75" spans="2:5">
+    <row r="125" ht="15.3" spans="2:5">
       <c r="B125" s="11"/>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
       <c r="E125" s="2"/>
     </row>
-    <row r="126" ht="15.75" spans="2:5">
+    <row r="126" ht="15.3" spans="2:5">
       <c r="B126" s="11"/>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
       <c r="E126" s="2"/>
     </row>
-    <row r="127" ht="15.75" spans="2:5">
+    <row r="127" ht="15.3" spans="2:5">
       <c r="B127" s="11"/>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
       <c r="E127" s="2"/>
     </row>
-    <row r="128" ht="15.75" spans="2:5">
+    <row r="128" ht="15.3" spans="2:5">
       <c r="B128" s="11"/>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
       <c r="E128" s="2"/>
     </row>
-    <row r="129" ht="15.75" spans="2:5">
+    <row r="129" ht="15.3" spans="2:5">
       <c r="B129" s="11"/>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
       <c r="E129" s="2"/>
     </row>
-    <row r="130" ht="15.75" spans="2:5">
+    <row r="130" ht="15.3" spans="2:5">
       <c r="B130" s="11"/>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
       <c r="E130" s="2"/>
     </row>
-    <row r="131" ht="15.75" spans="2:5">
+    <row r="131" ht="15.3" spans="2:5">
       <c r="B131" s="11"/>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
       <c r="E131" s="2"/>
     </row>
-    <row r="132" ht="15.75" spans="2:5">
+    <row r="132" ht="15.3" spans="2:5">
       <c r="B132" s="11"/>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
       <c r="E132" s="2"/>
     </row>
-    <row r="133" ht="15.75" spans="2:5">
+    <row r="133" ht="15.3" spans="2:5">
       <c r="B133" s="11"/>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
       <c r="E133" s="2"/>
     </row>
-    <row r="134" ht="15.75" spans="2:5">
+    <row r="134" ht="15.3" spans="2:5">
       <c r="B134" s="11"/>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
       <c r="E134" s="2"/>
     </row>
-    <row r="135" ht="15.75" spans="2:5">
+    <row r="135" ht="15.3" spans="2:5">
       <c r="B135" s="11"/>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
       <c r="E135" s="2"/>
     </row>
-    <row r="136" ht="15.75" spans="2:5">
+    <row r="136" ht="15.3" spans="2:5">
       <c r="B136" s="11"/>
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
       <c r="E136" s="2"/>
     </row>
-    <row r="137" ht="15.75" spans="2:5">
+    <row r="137" ht="15.3" spans="2:5">
       <c r="B137" s="11"/>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
       <c r="E137" s="2"/>
     </row>
-    <row r="138" ht="15.75" spans="2:5">
+    <row r="138" ht="15.3" spans="2:5">
       <c r="B138" s="11"/>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
       <c r="E138" s="2"/>
     </row>
-    <row r="139" ht="15.75" spans="2:5">
+    <row r="139" ht="15.3" spans="2:5">
       <c r="B139" s="11"/>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
       <c r="E139" s="2"/>
     </row>
-    <row r="140" ht="15.75" spans="2:5">
+    <row r="140" ht="15.3" spans="2:5">
       <c r="B140" s="11"/>
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
       <c r="E140" s="2"/>
     </row>
-    <row r="141" ht="15.75" spans="2:5">
+    <row r="141" ht="15.3" spans="2:5">
       <c r="B141" s="11"/>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
       <c r="E141" s="2"/>
     </row>
-    <row r="142" ht="15.75" spans="2:5">
+    <row r="142" ht="15.3" spans="2:5">
       <c r="B142" s="11"/>
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
       <c r="E142" s="2"/>
     </row>
-    <row r="143" ht="15.75" spans="2:5">
+    <row r="143" ht="15.3" spans="2:5">
       <c r="B143" s="11"/>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
       <c r="E143" s="2"/>
     </row>
-    <row r="144" ht="15.75" spans="2:5">
+    <row r="144" ht="15.3" spans="2:5">
       <c r="B144" s="11"/>
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
       <c r="E144" s="2"/>
     </row>
-    <row r="145" ht="15.75" spans="2:5">
+    <row r="145" ht="15.3" spans="2:5">
       <c r="B145" s="11"/>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
       <c r="E145" s="2"/>
     </row>
-    <row r="146" ht="15.75" spans="2:5">
+    <row r="146" ht="15.3" spans="2:5">
       <c r="B146" s="11"/>
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
       <c r="E146" s="2"/>
     </row>
-    <row r="147" ht="15.75" spans="2:5">
+    <row r="147" ht="15.3" spans="2:5">
       <c r="B147" s="11"/>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
       <c r="E147" s="2"/>
     </row>
-    <row r="148" ht="15.75" spans="2:5">
+    <row r="148" ht="15.3" spans="2:5">
       <c r="B148" s="11"/>
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
       <c r="E148" s="2"/>
     </row>
-    <row r="149" ht="15.75" spans="2:5">
+    <row r="149" ht="15.3" spans="2:5">
       <c r="B149" s="11"/>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
       <c r="E149" s="2"/>
     </row>
-    <row r="150" ht="15.75" spans="2:5">
+    <row r="150" ht="15.3" spans="2:5">
       <c r="B150" s="11"/>
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
       <c r="E150" s="2"/>
     </row>
-    <row r="151" ht="15.75" spans="2:5">
+    <row r="151" ht="15.3" spans="2:5">
       <c r="B151" s="11"/>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
       <c r="E151" s="2"/>
     </row>
-    <row r="152" ht="15.75" spans="2:5">
+    <row r="152" ht="15.3" spans="2:5">
       <c r="B152" s="11"/>
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
       <c r="E152" s="2"/>
     </row>
-    <row r="153" ht="15.75" spans="2:5">
+    <row r="153" ht="15.3" spans="2:5">
       <c r="B153" s="11"/>
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
       <c r="E153" s="2"/>
     </row>
-    <row r="154" ht="15.75" spans="2:5">
+    <row r="154" ht="15.3" spans="2:5">
       <c r="B154" s="11"/>
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
       <c r="E154" s="2"/>
     </row>
-    <row r="155" ht="15.75" spans="2:5">
+    <row r="155" ht="15.3" spans="2:5">
       <c r="B155" s="11"/>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
       <c r="E155" s="2"/>
     </row>
-    <row r="156" ht="15.75" spans="2:5">
+    <row r="156" ht="15.3" spans="2:5">
       <c r="B156" s="11"/>
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
       <c r="E156" s="2"/>
     </row>
-    <row r="157" ht="15.75" spans="2:5">
+    <row r="157" ht="15.3" spans="2:5">
       <c r="B157" s="11"/>
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
       <c r="E157" s="2"/>
     </row>
-    <row r="158" ht="15.75" spans="2:5">
+    <row r="158" ht="15.3" spans="2:5">
       <c r="B158" s="11"/>
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
       <c r="E158" s="2"/>
     </row>
-    <row r="159" ht="15.75" spans="2:5">
+    <row r="159" ht="15.3" spans="2:5">
       <c r="B159" s="11"/>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
       <c r="E159" s="2"/>
     </row>
-    <row r="160" ht="15.75" spans="2:5">
+    <row r="160" ht="15.3" spans="2:5">
       <c r="B160" s="11"/>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
       <c r="E160" s="2"/>
     </row>
-    <row r="161" ht="15.75" spans="2:5">
+    <row r="161" ht="15.3" spans="2:5">
       <c r="B161" s="11"/>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
       <c r="E161" s="2"/>
     </row>
-    <row r="162" ht="15.75" spans="2:5">
+    <row r="162" ht="15.3" spans="2:5">
       <c r="B162" s="11"/>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
       <c r="E162" s="2"/>
     </row>
-    <row r="163" ht="15.75" spans="2:5">
+    <row r="163" ht="15.3" spans="2:5">
       <c r="B163" s="11"/>
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
       <c r="E163" s="2"/>
     </row>
-    <row r="164" ht="15.75" spans="2:5">
+    <row r="164" ht="15.3" spans="2:5">
       <c r="B164" s="11"/>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
       <c r="E164" s="2"/>
     </row>
-    <row r="165" ht="15.75" spans="2:5">
+    <row r="165" ht="15.3" spans="2:5">
       <c r="B165" s="11"/>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
       <c r="E165" s="2"/>
     </row>
-    <row r="166" ht="15.75" spans="2:5">
+    <row r="166" ht="15.3" spans="2:5">
       <c r="B166" s="11"/>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
       <c r="E166" s="2"/>
     </row>
-    <row r="167" ht="15.75" spans="2:5">
+    <row r="167" ht="15.3" spans="2:5">
       <c r="B167" s="11"/>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
       <c r="E167" s="2"/>
     </row>
-    <row r="168" ht="15.75" spans="2:5">
+    <row r="168" ht="15.3" spans="2:5">
       <c r="B168" s="11"/>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
       <c r="E168" s="2"/>
     </row>
-    <row r="169" ht="15.75" spans="2:5">
+    <row r="169" ht="15.3" spans="2:5">
       <c r="B169" s="11"/>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
       <c r="E169" s="2"/>
     </row>
-    <row r="170" ht="15.75" spans="2:5">
+    <row r="170" ht="15.3" spans="2:5">
       <c r="B170" s="11"/>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
       <c r="E170" s="2"/>
     </row>
-    <row r="171" ht="15.75" spans="2:5">
+    <row r="171" ht="15.3" spans="2:5">
       <c r="B171" s="11"/>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
       <c r="E171" s="2"/>
     </row>
-    <row r="172" ht="15.75" spans="2:5">
+    <row r="172" ht="15.3" spans="2:5">
       <c r="B172" s="11"/>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
       <c r="E172" s="2"/>
     </row>
-    <row r="173" ht="15.75" spans="2:5">
+    <row r="173" ht="15.3" spans="2:5">
       <c r="B173" s="11"/>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
       <c r="E173" s="2"/>
     </row>
-    <row r="174" ht="15.75" spans="2:5">
+    <row r="174" ht="15.3" spans="2:5">
       <c r="B174" s="11"/>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
       <c r="E174" s="2"/>
     </row>
-    <row r="175" ht="15.75" spans="2:5">
+    <row r="175" ht="15.3" spans="2:5">
       <c r="B175" s="11"/>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
       <c r="E175" s="2"/>
     </row>
-    <row r="176" ht="15.75" spans="2:5">
+    <row r="176" ht="15.3" spans="2:5">
       <c r="B176" s="11"/>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
       <c r="E176" s="2"/>
     </row>
-    <row r="177" ht="15.75" spans="2:5">
+    <row r="177" ht="15.3" spans="2:5">
       <c r="B177" s="11"/>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
       <c r="E177" s="2"/>
     </row>
-    <row r="178" ht="15.75" spans="2:5">
+    <row r="178" ht="15.3" spans="2:5">
       <c r="B178" s="11"/>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
       <c r="E178" s="2"/>
     </row>
-    <row r="179" ht="15.75" spans="2:5">
+    <row r="179" ht="15.3" spans="2:5">
       <c r="B179" s="11"/>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
       <c r="E179" s="2"/>
     </row>
-    <row r="180" ht="15.75" spans="2:5">
+    <row r="180" ht="15.3" spans="2:5">
       <c r="B180" s="11"/>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
       <c r="E180" s="2"/>
     </row>
-    <row r="181" ht="15.75" spans="2:5">
+    <row r="181" ht="15.3" spans="2:5">
       <c r="B181" s="11"/>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
       <c r="E181" s="2"/>
     </row>
-    <row r="182" ht="15.75" spans="2:5">
+    <row r="182" ht="15.3" spans="2:5">
       <c r="B182" s="11"/>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
       <c r="E182" s="2"/>
     </row>
-    <row r="183" ht="15.75" spans="2:5">
+    <row r="183" ht="15.3" spans="2:5">
       <c r="B183" s="11"/>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
       <c r="E183" s="2"/>
     </row>
-    <row r="184" ht="15.75" spans="2:5">
+    <row r="184" ht="15.3" spans="2:5">
       <c r="B184" s="11"/>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
       <c r="E184" s="2"/>
     </row>
-    <row r="185" ht="15.75" spans="2:5">
+    <row r="185" ht="15.3" spans="2:5">
       <c r="B185" s="11"/>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
       <c r="E185" s="2"/>
     </row>
-    <row r="186" ht="15.75" spans="2:5">
+    <row r="186" ht="15.3" spans="2:5">
       <c r="B186" s="11"/>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
       <c r="E186" s="2"/>
     </row>
-    <row r="187" ht="15.75" spans="2:5">
+    <row r="187" ht="15.3" spans="2:5">
       <c r="B187" s="11"/>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
       <c r="E187" s="2"/>
     </row>
-    <row r="188" ht="15.75" spans="2:5">
+    <row r="188" ht="15.3" spans="2:5">
       <c r="B188" s="11"/>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
       <c r="E188" s="2"/>
     </row>
-    <row r="189" ht="15.75" spans="2:5">
+    <row r="189" ht="15.3" spans="2:5">
       <c r="B189" s="11"/>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
       <c r="E189" s="2"/>
     </row>
-    <row r="190" ht="15.75" spans="2:5">
+    <row r="190" ht="15.3" spans="2:5">
       <c r="B190" s="11"/>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
       <c r="E190" s="2"/>
     </row>
-    <row r="191" ht="15.75" spans="2:5">
+    <row r="191" ht="15.3" spans="2:5">
       <c r="B191" s="11"/>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
       <c r="E191" s="2"/>
     </row>
-    <row r="192" ht="15.75" spans="2:5">
+    <row r="192" ht="15.3" spans="2:5">
       <c r="B192" s="11"/>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
       <c r="E192" s="2"/>
     </row>
-    <row r="193" ht="15.75" spans="2:5">
+    <row r="193" ht="15.3" spans="2:5">
       <c r="B193" s="11"/>
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
       <c r="E193" s="2"/>
     </row>
-    <row r="194" ht="15.75" spans="2:5">
+    <row r="194" ht="15.3" spans="2:5">
       <c r="B194" s="11"/>
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
       <c r="E194" s="2"/>
     </row>
-    <row r="195" ht="15.75" spans="2:5">
+    <row r="195" ht="15.3" spans="2:5">
       <c r="B195" s="11"/>
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
       <c r="E195" s="2"/>
     </row>
-    <row r="196" ht="15.75" spans="2:5">
+    <row r="196" ht="15.3" spans="2:5">
       <c r="B196" s="11"/>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
       <c r="E196" s="2"/>
     </row>
-    <row r="197" ht="15.75" spans="2:5">
+    <row r="197" ht="15.3" spans="2:5">
       <c r="B197" s="11"/>
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
       <c r="E197" s="2"/>
     </row>
-    <row r="198" ht="15.75" spans="2:5">
+    <row r="198" ht="15.3" spans="2:5">
       <c r="B198" s="11"/>
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
       <c r="E198" s="2"/>
     </row>
-    <row r="199" ht="15.75" spans="2:5">
+    <row r="199" ht="15.3" spans="2:5">
       <c r="B199" s="11"/>
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
       <c r="E199" s="2"/>
     </row>
-    <row r="200" ht="15.75" spans="2:5">
+    <row r="200" ht="15.3" spans="2:5">
       <c r="B200" s="11"/>
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
       <c r="E200" s="2"/>
     </row>
-    <row r="201" ht="15.75" spans="2:5">
+    <row r="201" ht="15.3" spans="2:5">
       <c r="B201" s="11"/>
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
       <c r="E201" s="2"/>
     </row>
-    <row r="202" ht="15.75" spans="2:5">
+    <row r="202" ht="15.3" spans="2:5">
       <c r="B202" s="11"/>
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
       <c r="E202" s="2"/>
     </row>
-    <row r="203" ht="15.75" spans="2:5">
+    <row r="203" ht="15.3" spans="2:5">
       <c r="B203" s="11"/>
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
       <c r="E203" s="2"/>
     </row>
-    <row r="204" ht="15.75" spans="2:5">
+    <row r="204" ht="15.3" spans="2:5">
       <c r="B204" s="11"/>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
       <c r="E204" s="2"/>
     </row>
-    <row r="205" ht="15.75" spans="2:5">
+    <row r="205" ht="15.3" spans="2:5">
       <c r="B205" s="11"/>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
       <c r="E205" s="2"/>
     </row>
-    <row r="206" ht="15.75" spans="2:5">
+    <row r="206" ht="15.3" spans="2:5">
       <c r="B206" s="11"/>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
       <c r="E206" s="2"/>
     </row>
-    <row r="207" ht="15.75" spans="2:5">
+    <row r="207" ht="15.3" spans="2:5">
       <c r="B207" s="11"/>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
       <c r="E207" s="2"/>
     </row>
-    <row r="208" ht="15.75" spans="2:5">
+    <row r="208" ht="15.3" spans="2:5">
       <c r="B208" s="11"/>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
       <c r="E208" s="2"/>
     </row>
-    <row r="209" ht="15.75" spans="2:5">
+    <row r="209" ht="15.3" spans="2:5">
       <c r="B209" s="11"/>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
       <c r="E209" s="2"/>
     </row>
-    <row r="210" ht="15.75" spans="2:5">
+    <row r="210" ht="15.3" spans="2:5">
       <c r="B210" s="11"/>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
       <c r="E210" s="2"/>
     </row>
-    <row r="211" ht="15.75" spans="2:5">
+    <row r="211" ht="15.3" spans="2:5">
       <c r="B211" s="11"/>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
       <c r="E211" s="2"/>
     </row>
-    <row r="212" ht="15.75" spans="2:5">
+    <row r="212" ht="15.3" spans="2:5">
       <c r="B212" s="11"/>
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
       <c r="E212" s="2"/>
     </row>
-    <row r="213" ht="15.75" spans="2:5">
+    <row r="213" ht="15.3" spans="2:5">
       <c r="B213" s="11"/>
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
       <c r="E213" s="2"/>
     </row>
-    <row r="214" ht="15.75" spans="2:5">
+    <row r="214" ht="15.3" spans="2:5">
       <c r="B214" s="11"/>
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
       <c r="E214" s="2"/>
     </row>
-    <row r="215" ht="15.75" spans="2:5">
+    <row r="215" ht="15.3" spans="2:5">
       <c r="B215" s="11"/>
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
       <c r="E215" s="2"/>
     </row>
-    <row r="216" ht="15.75" spans="2:5">
+    <row r="216" ht="15.3" spans="2:5">
       <c r="B216" s="11"/>
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
       <c r="E216" s="2"/>
     </row>
-    <row r="217" ht="15.75" spans="2:5">
+    <row r="217" ht="15.3" spans="2:5">
       <c r="B217" s="11"/>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
       <c r="E217" s="2"/>
     </row>
-    <row r="218" ht="15.75" spans="2:5">
+    <row r="218" ht="15.3" spans="2:5">
       <c r="B218" s="11"/>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
       <c r="E218" s="2"/>
     </row>
-    <row r="219" ht="15.75" spans="2:5">
+    <row r="219" ht="15.3" spans="2:5">
       <c r="B219" s="11"/>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
       <c r="E219" s="2"/>
     </row>
-    <row r="220" ht="15.75" spans="2:5">
+    <row r="220" ht="15.3" spans="2:5">
       <c r="B220" s="11"/>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
       <c r="E220" s="2"/>
     </row>
-    <row r="221" ht="15.75" spans="2:5">
+    <row r="221" ht="15.3" spans="2:5">
       <c r="B221" s="11"/>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
       <c r="E221" s="2"/>
     </row>
-    <row r="222" ht="15.75" spans="2:5">
+    <row r="222" ht="15.3" spans="2:5">
       <c r="B222" s="11"/>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
       <c r="E222" s="2"/>
     </row>
-    <row r="223" ht="15.75" spans="2:5">
+    <row r="223" ht="15.3" spans="2:5">
       <c r="B223" s="11"/>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
       <c r="E223" s="2"/>
     </row>
-    <row r="224" ht="15.75" spans="2:5">
+    <row r="224" ht="15.3" spans="2:5">
       <c r="B224" s="11"/>
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
       <c r="E224" s="2"/>
     </row>
-    <row r="225" ht="15.75" spans="2:5">
+    <row r="225" ht="15.3" spans="2:5">
       <c r="B225" s="11"/>
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
       <c r="E225" s="2"/>
     </row>
-    <row r="226" ht="15.75" spans="2:5">
+    <row r="226" ht="15.3" spans="2:5">
       <c r="B226" s="11"/>
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
       <c r="E226" s="2"/>
     </row>
-    <row r="227" ht="15.75" spans="2:5">
+    <row r="227" ht="15.3" spans="2:5">
       <c r="B227" s="11"/>
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
       <c r="E227" s="2"/>
     </row>
-    <row r="228" ht="15.75" spans="2:5">
+    <row r="228" ht="15.3" spans="2:5">
       <c r="B228" s="11"/>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
       <c r="E228" s="2"/>
     </row>
-    <row r="229" ht="15.75" spans="2:5">
+    <row r="229" ht="15.3" spans="2:5">
       <c r="B229" s="11"/>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
       <c r="E229" s="2"/>
     </row>
-    <row r="230" ht="15.75" spans="2:5">
+    <row r="230" ht="15.3" spans="2:5">
       <c r="B230" s="11"/>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
       <c r="E230" s="2"/>
     </row>
-    <row r="231" ht="15.75" spans="2:5">
+    <row r="231" ht="15.3" spans="2:5">
       <c r="B231" s="11"/>
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
       <c r="E231" s="2"/>
     </row>
-    <row r="232" ht="15.75" spans="2:5">
+    <row r="232" ht="15.3" spans="2:5">
       <c r="B232" s="11"/>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
       <c r="E232" s="2"/>
     </row>
-    <row r="233" ht="15.75" spans="2:5">
+    <row r="233" ht="15.3" spans="2:5">
       <c r="B233" s="11"/>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
       <c r="E233" s="2"/>
     </row>
-    <row r="234" ht="15.75" spans="2:5">
+    <row r="234" ht="15.3" spans="2:5">
       <c r="B234" s="11"/>
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
       <c r="E234" s="2"/>
     </row>
-    <row r="235" ht="15.75" spans="2:5">
+    <row r="235" ht="15.3" spans="2:5">
       <c r="B235" s="11"/>
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
       <c r="E235" s="2"/>
     </row>
-    <row r="236" ht="15.75" spans="2:5">
+    <row r="236" ht="15.3" spans="2:5">
       <c r="B236" s="11"/>
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
       <c r="E236" s="2"/>
     </row>
-    <row r="237" ht="15.75" spans="2:5">
+    <row r="237" ht="15.3" spans="2:5">
       <c r="B237" s="11"/>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
       <c r="E237" s="2"/>
     </row>
-    <row r="238" ht="15.75" spans="2:5">
+    <row r="238" ht="15.3" spans="2:5">
       <c r="B238" s="11"/>
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
       <c r="E238" s="2"/>
     </row>
-    <row r="239" ht="15.75" spans="2:5">
+    <row r="239" ht="15.3" spans="2:5">
       <c r="B239" s="11"/>
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
       <c r="E239" s="2"/>
     </row>
-    <row r="240" ht="15.75" spans="2:5">
+    <row r="240" ht="15.3" spans="2:5">
       <c r="B240" s="11"/>
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
       <c r="E240" s="2"/>
     </row>
-    <row r="241" ht="15.75" spans="2:5">
+    <row r="241" ht="15.3" spans="2:5">
       <c r="B241" s="11"/>
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
       <c r="E241" s="2"/>
     </row>
-    <row r="242" ht="15.75" spans="2:5">
+    <row r="242" ht="15.3" spans="2:5">
       <c r="B242" s="11"/>
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
       <c r="E242" s="2"/>
     </row>
-    <row r="243" ht="15.75" spans="2:5">
+    <row r="243" ht="15.3" spans="2:5">
       <c r="B243" s="11"/>
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
       <c r="E243" s="2"/>
     </row>
-    <row r="244" ht="15.75" spans="2:5">
+    <row r="244" ht="15.3" spans="2:5">
       <c r="B244" s="11"/>
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
       <c r="E244" s="2"/>
     </row>
-    <row r="245" ht="15.75" spans="2:5">
+    <row r="245" ht="15.3" spans="2:5">
       <c r="B245" s="11"/>
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
       <c r="E245" s="2"/>
     </row>
-    <row r="246" ht="15.75" spans="2:5">
+    <row r="246" ht="15.3" spans="2:5">
       <c r="B246" s="11"/>
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
       <c r="E246" s="2"/>
     </row>
-    <row r="247" ht="15.75" spans="2:5">
+    <row r="247" ht="15.3" spans="2:5">
       <c r="B247" s="11"/>
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
       <c r="E247" s="2"/>
     </row>
-    <row r="248" ht="15.75" spans="2:5">
+    <row r="248" ht="15.3" spans="2:5">
       <c r="B248" s="11"/>
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
       <c r="E248" s="2"/>
     </row>
-    <row r="249" ht="15.75" spans="2:5">
+    <row r="249" ht="15.3" spans="2:5">
       <c r="B249" s="11"/>
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
       <c r="E249" s="2"/>
     </row>
-    <row r="250" ht="15.75" spans="2:5">
+    <row r="250" ht="15.3" spans="2:5">
       <c r="B250" s="11"/>
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
       <c r="E250" s="2"/>
     </row>
-    <row r="251" ht="15.75" spans="2:5">
+    <row r="251" ht="15.3" spans="2:5">
       <c r="B251" s="11"/>
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
       <c r="E251" s="2"/>
     </row>
-    <row r="252" ht="15.75" spans="2:5">
+    <row r="252" ht="15.3" spans="2:5">
       <c r="B252" s="11"/>
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
       <c r="E252" s="2"/>
     </row>
-    <row r="253" ht="15.75" spans="2:5">
+    <row r="253" ht="15.3" spans="2:5">
       <c r="B253" s="11"/>
       <c r="C253" s="7"/>
       <c r="D253" s="7"/>
       <c r="E253" s="2"/>
     </row>
-    <row r="254" ht="15.75" spans="2:5">
+    <row r="254" ht="15.3" spans="2:5">
       <c r="B254" s="11"/>
       <c r="C254" s="7"/>
       <c r="D254" s="7"/>
       <c r="E254" s="2"/>
     </row>
-    <row r="255" ht="15.75" spans="2:5">
+    <row r="255" ht="15.3" spans="2:5">
       <c r="B255" s="11"/>
       <c r="C255" s="7"/>
       <c r="D255" s="7"/>
       <c r="E255" s="2"/>
     </row>
-    <row r="256" ht="15.75" spans="2:5">
+    <row r="256" ht="15.3" spans="2:5">
       <c r="B256" s="11"/>
       <c r="C256" s="7"/>
       <c r="D256" s="7"/>
       <c r="E256" s="2"/>
     </row>
-    <row r="257" ht="15.75" spans="2:5">
+    <row r="257" ht="15.3" spans="2:5">
       <c r="B257" s="11"/>
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
       <c r="E257" s="2"/>
     </row>
-    <row r="258" ht="15.75" spans="2:5">
+    <row r="258" ht="15.3" spans="2:5">
       <c r="B258" s="11"/>
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
       <c r="E258" s="2"/>
     </row>
-    <row r="259" ht="15.75" spans="2:5">
+    <row r="259" ht="15.3" spans="2:5">
       <c r="B259" s="11"/>
       <c r="C259" s="7"/>
       <c r="D259" s="7"/>
       <c r="E259" s="2"/>
     </row>
-    <row r="260" ht="15.75" spans="2:5">
+    <row r="260" ht="15.3" spans="2:5">
       <c r="B260" s="11"/>
       <c r="C260" s="7"/>
       <c r="D260" s="7"/>
       <c r="E260" s="2"/>
     </row>
-    <row r="261" ht="15.75" spans="2:5">
+    <row r="261" ht="15.3" spans="2:5">
       <c r="B261" s="11"/>
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
       <c r="E261" s="2"/>
     </row>
-    <row r="262" ht="15.75" spans="2:5">
+    <row r="262" ht="15.3" spans="2:5">
       <c r="B262" s="11"/>
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
       <c r="E262" s="2"/>
     </row>
-    <row r="263" ht="15.75" spans="2:5">
+    <row r="263" ht="15.3" spans="2:5">
       <c r="B263" s="11"/>
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
       <c r="E263" s="2"/>
     </row>
-    <row r="264" ht="15.75" spans="2:5">
+    <row r="264" ht="15.3" spans="2:5">
       <c r="B264" s="11"/>
       <c r="C264" s="7"/>
       <c r="D264" s="7"/>
       <c r="E264" s="2"/>
     </row>
-    <row r="265" ht="15.75" spans="2:5">
+    <row r="265" ht="15.3" spans="2:5">
       <c r="B265" s="11"/>
       <c r="C265" s="7"/>
       <c r="D265" s="7"/>
       <c r="E265" s="2"/>
     </row>
-    <row r="266" ht="15.75" spans="2:5">
+    <row r="266" ht="15.3" spans="2:5">
       <c r="B266" s="11"/>
       <c r="C266" s="7"/>
       <c r="D266" s="7"/>
       <c r="E266" s="2"/>
     </row>
-    <row r="267" ht="15.75" spans="2:5">
+    <row r="267" ht="15.3" spans="2:5">
       <c r="B267" s="11"/>
       <c r="C267" s="7"/>
       <c r="D267" s="7"/>
       <c r="E267" s="2"/>
     </row>
-    <row r="268" ht="15.75" spans="2:5">
+    <row r="268" ht="15.3" spans="2:5">
       <c r="B268" s="11"/>
       <c r="C268" s="7"/>
       <c r="D268" s="7"/>
       <c r="E268" s="2"/>
     </row>
-    <row r="269" ht="15.75" spans="2:5">
+    <row r="269" ht="15.3" spans="2:5">
       <c r="B269" s="11"/>
       <c r="C269" s="7"/>
       <c r="D269" s="7"/>
       <c r="E269" s="2"/>
     </row>
-    <row r="270" ht="15.75" spans="2:5">
+    <row r="270" ht="15.3" spans="2:5">
       <c r="B270" s="11"/>
       <c r="C270" s="7"/>
       <c r="D270" s="7"/>
       <c r="E270" s="2"/>
     </row>
-    <row r="271" ht="15.75" spans="2:5">
+    <row r="271" ht="15.3" spans="2:5">
       <c r="B271" s="11"/>
       <c r="C271" s="7"/>
       <c r="D271" s="7"/>
       <c r="E271" s="2"/>
     </row>
-    <row r="272" ht="15.75" spans="2:5">
+    <row r="272" ht="15.3" spans="2:5">
       <c r="B272" s="11"/>
       <c r="C272" s="7"/>
       <c r="D272" s="7"/>
       <c r="E272" s="2"/>
     </row>
-    <row r="273" ht="15.75" spans="2:5">
+    <row r="273" ht="15.3" spans="2:5">
       <c r="B273" s="11"/>
       <c r="C273" s="7"/>
       <c r="D273" s="7"/>
       <c r="E273" s="2"/>
     </row>
-    <row r="274" ht="15.75" spans="2:5">
+    <row r="274" ht="15.3" spans="2:5">
       <c r="B274" s="11"/>
       <c r="C274" s="7"/>
       <c r="D274" s="7"/>
       <c r="E274" s="2"/>
     </row>
-    <row r="275" ht="15.75" spans="2:5">
+    <row r="275" ht="15.3" spans="2:5">
       <c r="B275" s="11"/>
       <c r="C275" s="7"/>
       <c r="D275" s="7"/>
       <c r="E275" s="2"/>
     </row>
-    <row r="276" ht="15.75" spans="2:5">
+    <row r="276" ht="15.3" spans="2:5">
       <c r="B276" s="11"/>
       <c r="C276" s="7"/>
       <c r="D276" s="7"/>
       <c r="E276" s="2"/>
     </row>
-    <row r="277" ht="15.75" spans="2:5">
+    <row r="277" ht="15.3" spans="2:5">
       <c r="B277" s="11"/>
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
       <c r="E277" s="2"/>
     </row>
-    <row r="278" ht="15.75" spans="2:5">
+    <row r="278" ht="15.3" spans="2:5">
       <c r="B278" s="11"/>
       <c r="C278" s="7"/>
       <c r="D278" s="7"/>
       <c r="E278" s="2"/>
     </row>
-    <row r="279" ht="15.75" spans="2:5">
+    <row r="279" ht="15.3" spans="2:5">
       <c r="B279" s="11"/>
       <c r="C279" s="7"/>
       <c r="D279" s="7"/>
       <c r="E279" s="2"/>
     </row>
-    <row r="280" ht="15.75" spans="2:5">
+    <row r="280" ht="15.3" spans="2:5">
       <c r="B280" s="11"/>
       <c r="C280" s="7"/>
       <c r="D280" s="7"/>
       <c r="E280" s="2"/>
     </row>
-    <row r="281" ht="15.75" spans="2:5">
+    <row r="281" ht="15.3" spans="2:5">
       <c r="B281" s="11"/>
       <c r="C281" s="7"/>
       <c r="D281" s="7"/>
       <c r="E281" s="2"/>
     </row>
-    <row r="282" ht="15.75" spans="2:5">
+    <row r="282" ht="15.3" spans="2:5">
       <c r="B282" s="11"/>
       <c r="C282" s="7"/>
       <c r="D282" s="7"/>
       <c r="E282" s="2"/>
     </row>
-    <row r="283" ht="15.75" spans="2:5">
+    <row r="283" ht="15.3" spans="2:5">
       <c r="B283" s="11"/>
       <c r="C283" s="7"/>
       <c r="D283" s="7"/>
       <c r="E283" s="2"/>
     </row>
-    <row r="284" ht="15.75" spans="2:5">
+    <row r="284" ht="15.3" spans="2:5">
       <c r="B284" s="11"/>
       <c r="C284" s="7"/>
       <c r="D284" s="7"/>
       <c r="E284" s="2"/>
     </row>
-    <row r="285" ht="15.75" spans="2:5">
+    <row r="285" ht="15.3" spans="2:5">
       <c r="B285" s="11"/>
       <c r="C285" s="7"/>
       <c r="D285" s="7"/>
       <c r="E285" s="2"/>
     </row>
-    <row r="286" ht="15.75" spans="2:5">
+    <row r="286" ht="15.3" spans="2:5">
       <c r="B286" s="11"/>
       <c r="C286" s="7"/>
       <c r="D286" s="7"/>
       <c r="E286" s="2"/>
     </row>
-    <row r="287" ht="15.75" spans="2:5">
+    <row r="287" ht="15.3" spans="2:5">
       <c r="B287" s="11"/>
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
       <c r="E287" s="2"/>
     </row>
-    <row r="288" ht="15.75" spans="2:5">
+    <row r="288" ht="15.3" spans="2:5">
       <c r="B288" s="11"/>
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
       <c r="E288" s="2"/>
     </row>
-    <row r="289" ht="15.75" spans="2:5">
+    <row r="289" ht="15.3" spans="2:5">
       <c r="B289" s="11"/>
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
       <c r="E289" s="2"/>
     </row>
-    <row r="290" ht="15.75" spans="2:5">
+    <row r="290" ht="15.3" spans="2:5">
       <c r="B290" s="11"/>
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
       <c r="E290" s="2"/>
     </row>
-    <row r="291" ht="15.75" spans="2:5">
+    <row r="291" ht="15.3" spans="2:5">
       <c r="B291" s="11"/>
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
       <c r="E291" s="2"/>
     </row>
-    <row r="292" ht="15.75" spans="2:5">
+    <row r="292" ht="15.3" spans="2:5">
       <c r="B292" s="11"/>
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
       <c r="E292" s="2"/>
     </row>
-    <row r="293" ht="15"/>
+    <row r="293" ht="14.55"/>
   </sheetData>
   <conditionalFormatting sqref="C3:C292">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -3163,7 +3172,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="30.2166666666667" customWidth="1"/>
     <col min="2" max="2" width="14.5583333333333" style="1" customWidth="1"/>
@@ -3172,7 +3181,7 @@
     <col min="7" max="18" width="14.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:18">
+    <row r="1" ht="15.3" spans="1:18">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="2" t="s">
@@ -3200,7 +3209,7 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
     </row>
-    <row r="2" ht="15.75" spans="1:18">
+    <row r="2" ht="15.3" spans="1:18">
       <c r="A2" s="2"/>
       <c r="B2" s="7"/>
       <c r="C2" s="2"/>
@@ -3220,7 +3229,7 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" ht="15.75" spans="1:18">
+    <row r="3" ht="15.3" spans="1:18">
       <c r="A3" s="2"/>
       <c r="B3" s="7" t="s">
         <v>29</v>
@@ -3274,7 +3283,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:18">
+    <row r="4" ht="15.3" spans="1:18">
       <c r="A4" s="2"/>
       <c r="B4" s="9">
         <v>46281</v>
@@ -3328,7 +3337,7 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="5" ht="15.75" spans="1:18">
+    <row r="5" ht="15.3" spans="1:18">
       <c r="A5" s="11" t="s">
         <v>36</v>
       </c>
@@ -3352,7 +3361,7 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" ht="15.75" spans="1:18">
+    <row r="6" ht="15.3" spans="1:18">
       <c r="A6" s="11" t="s">
         <v>37</v>
       </c>
@@ -3376,7 +3385,7 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" ht="15.75" spans="1:18">
+    <row r="7" ht="15.3" spans="1:18">
       <c r="A7" s="11" t="s">
         <v>38</v>
       </c>
@@ -3400,15 +3409,15 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" ht="15.75" spans="1:18">
+    <row r="8" ht="15.3" spans="1:18">
       <c r="A8" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="12"/>
@@ -3426,7 +3435,7 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
     </row>
-    <row r="9" ht="15.75" spans="1:18">
+    <row r="9" ht="15.3" spans="1:18">
       <c r="A9" s="14" t="s">
         <v>40</v>
       </c>
@@ -3450,15 +3459,15 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" ht="15.75" spans="1:18">
+    <row r="10" ht="15.3" spans="1:18">
       <c r="A10" s="14" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="12"/>
@@ -3476,7 +3485,7 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" ht="15.75" spans="1:18">
+    <row r="11" ht="15.3" spans="1:18">
       <c r="A11" s="14" t="s">
         <v>42</v>
       </c>
@@ -3500,15 +3509,15 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" ht="15.75" spans="1:18">
+    <row r="12" ht="15.3" spans="1:18">
       <c r="A12" s="14" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="12"/>
@@ -3526,15 +3535,15 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" ht="15.75" spans="1:18">
+    <row r="13" ht="15.3" spans="1:18">
       <c r="A13" s="11" t="s">
         <v>44</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="12"/>
@@ -3552,7 +3561,7 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" ht="15.75" spans="1:18">
+    <row r="14" ht="15.3" spans="1:18">
       <c r="A14" s="14" t="s">
         <v>45</v>
       </c>
@@ -3576,13 +3585,13 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" ht="15.75" spans="1:18">
+    <row r="15" ht="15.3" spans="1:18">
       <c r="A15" s="14" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="12"/>
@@ -3600,13 +3609,13 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" ht="15.75" spans="1:18">
+    <row r="16" ht="15.3" spans="1:18">
       <c r="A16" s="14" t="s">
         <v>47</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="12"/>
@@ -3624,13 +3633,13 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" ht="15.75" spans="1:18">
+    <row r="17" ht="15.3" spans="1:18">
       <c r="A17" s="11" t="s">
         <v>48</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>5</v>
@@ -3652,13 +3661,13 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" ht="15.75" spans="1:18">
+    <row r="18" ht="15.3" spans="1:18">
       <c r="A18" s="14" t="s">
         <v>49</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -3680,7 +3689,7 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" ht="15.75" spans="1:18">
+    <row r="19" ht="15.3" spans="1:18">
       <c r="A19" s="14" t="s">
         <v>50</v>
       </c>
@@ -3708,7 +3717,7 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" ht="15.75" spans="1:18">
+    <row r="20" ht="15.3" spans="1:18">
       <c r="A20" s="14" t="s">
         <v>52</v>
       </c>
@@ -3736,7 +3745,7 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" ht="15.75" spans="1:18">
+    <row r="21" ht="15.3" spans="1:18">
       <c r="A21" s="11" t="s">
         <v>53</v>
       </c>
@@ -3764,7 +3773,7 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" ht="15.75" spans="1:18">
+    <row r="22" ht="15.3" spans="1:18">
       <c r="A22" s="14" t="s">
         <v>49</v>
       </c>
@@ -3792,7 +3801,7 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" ht="15.75" spans="1:18">
+    <row r="23" ht="15.3" spans="1:18">
       <c r="A23" s="14" t="s">
         <v>50</v>
       </c>
@@ -3820,7 +3829,7 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" ht="15.75" spans="1:18">
+    <row r="24" ht="15.3" spans="1:18">
       <c r="A24" s="14" t="s">
         <v>52</v>
       </c>
@@ -3834,7 +3843,7 @@
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
       <c r="G24" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>5</v>
@@ -3850,7 +3859,7 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" ht="15.75" spans="1:18">
+    <row r="25" ht="15.3" spans="1:18">
       <c r="A25" s="11" t="s">
         <v>54</v>
       </c>
@@ -3860,7 +3869,7 @@
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
       <c r="G25" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>5</v>
@@ -3876,7 +3885,7 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" ht="15.75" spans="1:18">
+    <row r="26" ht="15.3" spans="1:18">
       <c r="A26" s="14" t="s">
         <v>49</v>
       </c>
@@ -3886,7 +3895,7 @@
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
       <c r="G26" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>5</v>
@@ -3902,7 +3911,7 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" ht="15.75" spans="1:18">
+    <row r="27" ht="15.3" spans="1:18">
       <c r="A27" s="14" t="s">
         <v>50</v>
       </c>
@@ -3912,7 +3921,7 @@
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
       <c r="G27" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>5</v>
@@ -3928,7 +3937,7 @@
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" ht="15.75" spans="1:18">
+    <row r="28" ht="15.3" spans="1:18">
       <c r="A28" s="14" t="s">
         <v>52</v>
       </c>
@@ -3938,7 +3947,7 @@
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
       <c r="G28" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>5</v>
@@ -3954,7 +3963,7 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" ht="15"/>
+    <row r="29" ht="14.55"/>
   </sheetData>
   <conditionalFormatting sqref="B5:R28">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
